--- a/Starfront/文档/配置表/BattleSceneResource.xlsx
+++ b/Starfront/文档/配置表/BattleSceneResource.xlsx
@@ -2,9 +2,84 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d9329f5b19d40e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R48dae46a953740cd"/>
   </x:sheets>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>tc={B06584AD-BF26-477B-933B-67FA339C714A}</x:author>
+    <x:author>tc={EF59ECA6-DD71-4B60-9531-51F76551E60B}</x:author>
+    <x:author>tc={7E56C757-B849-462C-9620-4D1526292205}</x:author>
+    <x:author>tc={317BDBF5-A225-441C-B686-44864634979A}</x:author>
+    <x:author>tc={E9AF3B12-5578-4ADE-B0CD-2A82AF44F4B6}</x:author>
+    <x:author>tc={A29D137C-31B0-44FB-B8F4-C12ACA9969C2}</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="U1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    相对 Assets/Art/unpack/，省略固定 .png 后缀；普通区域灰度，中立原色。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="V1" authorId="1">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    同底图原点与尺寸；独立格线，不参与染色。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="W1" authorId="2">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    相对 Assets/Art/material/，省略 .mat；材质持有离线像素归属图。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="X1" authorId="3">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    设计坐标X右Y下；整图左上角在场景中的位置，与格心原点不同。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="Y1" authorId="4">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    静态美术规格，已烘焙进图片；运行时只供建筑、单位、阴影及跟随信息定位，禁止据此拼接/拉伸地形。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="Z1" authorId="5">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    静态美术规格，已烘焙进水洼；运行时不生成或移动岸壁。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1014,6 +1089,12 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="Starfront" id="{DEAA05B8-006E-4443-B875-7B006548178F}"/>
+</xltc:personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -1205,31 +1286,66 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="U1" dT="2026-10-27T10:16:36.913" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{B06584AD-BF26-477B-933B-67FA339C714A}">
+    <xltc:text>相对 Assets/Art/unpack/，省略固定 .png 后缀；普通区域灰度，中立原色。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="V1" dT="2026-10-27T10:16:36.913" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{EF59ECA6-DD71-4B60-9531-51F76551E60B}">
+    <xltc:text>同底图原点与尺寸；独立格线，不参与染色。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="W1" dT="2026-10-27T10:16:36.913" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{7E56C757-B849-462C-9620-4D1526292205}">
+    <xltc:text>相对 Assets/Art/material/，省略 .mat；材质持有离线像素归属图。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="X1" dT="2026-10-27T10:16:36.914" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{317BDBF5-A225-441C-B686-44864634979A}">
+    <xltc:text>设计坐标X右Y下；整图左上角在场景中的位置，与格心原点不同。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="Y1" dT="2026-10-27T10:16:36.914" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{E9AF3B12-5578-4ADE-B0CD-2A82AF44F4B6}">
+    <xltc:text>静态美术规格，已烘焙进图片；运行时只供建筑、单位、阴影及跟随信息定位，禁止据此拼接/拉伸地形。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="Z1" dT="2026-10-27T10:16:36.914" personId="{DEAA05B8-006E-4443-B875-7B006548178F}" id="{A29D137C-31B0-44FB-B8F4-C12ACA9969C2}">
+    <xltc:text>静态美术规格，已烘焙进水洼；运行时不生成或移动岸壁。</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" customWidth="1"/>
-    <x:col min="2" max="2" width="7" customWidth="1"/>
-    <x:col min="3" max="3" width="13.75" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="5" width="17.125" customWidth="1"/>
-    <x:col min="6" max="6" width="18.5" customWidth="1"/>
-    <x:col min="7" max="7" width="18.375" customWidth="1"/>
-    <x:col min="8" max="8" width="16" customWidth="1"/>
-    <x:col min="9" max="9" width="15.875" customWidth="1"/>
-    <x:col min="10" max="10" width="14.375" customWidth="1"/>
-    <x:col min="11" max="11" width="14" customWidth="1"/>
-    <x:col min="12" max="12" width="13.5" customWidth="1"/>
-    <x:col min="13" max="13" width="13.25" customWidth="1"/>
-    <x:col min="14" max="14" width="14.375" customWidth="1"/>
-    <x:col min="15" max="15" width="48.5" customWidth="1"/>
-    <x:col min="16" max="16" width="8.875" customWidth="1"/>
-    <x:col min="17" max="17" width="12.875" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="33" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="37" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="36" hidden="0" customWidth="1"/>
     <x:col min="18" max="19" width="10.875" customWidth="1"/>
-    <x:col min="20" max="20" width="12" customWidth="1"/>
-    <x:col min="21" max="21" width="48" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="48" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="48" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="13" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="28" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="33" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="15" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="22" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="22" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="14" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="14" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="18" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="16.5">
@@ -1282,13 +1398,37 @@
       <x:c r="S1" s="1"/>
       <x:c r="T1" s="1"/>
       <x:c r="U1" s="6" t="str">
-        <x:v>friendlyGroundResource</x:v>
+        <x:v>groundResource</x:v>
       </x:c>
       <x:c r="V1" s="6" t="str">
-        <x:v>enemyGroundResource</x:v>
+        <x:v>groundGridResource</x:v>
       </x:c>
       <x:c r="W1" s="6" t="str">
-        <x:v>neutralGroundResource</x:v>
+        <x:v>groundMaterialResource</x:v>
+      </x:c>
+      <x:c r="X1" s="6" t="str">
+        <x:v>groundOffset</x:v>
+      </x:c>
+      <x:c r="Y1" s="6" t="str">
+        <x:v>groundThickness</x:v>
+      </x:c>
+      <x:c r="Z1" s="6" t="str">
+        <x:v>waterDepth</x:v>
+      </x:c>
+      <x:c r="AA1" s="6" t="str">
+        <x:v>groundRed</x:v>
+      </x:c>
+      <x:c r="AB1" s="6" t="str">
+        <x:v>groundBlue</x:v>
+      </x:c>
+      <x:c r="AC1" s="6" t="str">
+        <x:v>groundTintStrength</x:v>
+      </x:c>
+      <x:c r="AD1" s="6" t="str">
+        <x:v>groundBrightness</x:v>
+      </x:c>
+      <x:c r="AE1" s="6" t="str">
+        <x:v>groundContrast</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="16.5">
@@ -1341,13 +1481,37 @@
       <x:c r="S2" s="2"/>
       <x:c r="T2" s="2"/>
       <x:c r="U2" s="7" t="str">
-        <x:v>己方通用地面</x:v>
+        <x:v>完整地块底图</x:v>
       </x:c>
       <x:c r="V2" s="7" t="str">
-        <x:v>敌方通用地面</x:v>
+        <x:v>独立地表格线</x:v>
       </x:c>
       <x:c r="W2" s="7" t="str">
-        <x:v>中立通用地面</x:v>
+        <x:v>地表染色材质</x:v>
+      </x:c>
+      <x:c r="X2" s="7" t="str">
+        <x:v>底图左上角X,Y</x:v>
+      </x:c>
+      <x:c r="Y2" s="7" t="str">
+        <x:v>静态地块厚度（像素）</x:v>
+      </x:c>
+      <x:c r="Z2" s="7" t="str">
+        <x:v>静态水洼深度（像素）</x:v>
+      </x:c>
+      <x:c r="AA2" s="7" t="str">
+        <x:v>敌方地表颜色</x:v>
+      </x:c>
+      <x:c r="AB2" s="7" t="str">
+        <x:v>己方地表颜色</x:v>
+      </x:c>
+      <x:c r="AC2" s="7" t="str">
+        <x:v>地表染色强度</x:v>
+      </x:c>
+      <x:c r="AD2" s="7" t="str">
+        <x:v>地表灰度亮度</x:v>
+      </x:c>
+      <x:c r="AE2" s="7" t="str">
+        <x:v>地表灰度对比度</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="16.5">
@@ -1407,6 +1571,30 @@
       </x:c>
       <x:c r="W3" s="8" t="str">
         <x:v>string</x:v>
+      </x:c>
+      <x:c r="X3" s="8" t="str">
+        <x:v>vector2</x:v>
+      </x:c>
+      <x:c r="Y3" s="8" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Z3" s="8" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AA3" s="8" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AB3" s="8" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AC3" s="8" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AD3" s="8" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AE3" s="8" t="str">
+        <x:v>float</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16.5">
@@ -1447,6 +1635,14 @@
       <x:c r="U4" s="6"/>
       <x:c r="V4" s="6"/>
       <x:c r="W4" s="6"/>
+      <x:c r="X4" s="6"/>
+      <x:c r="Y4" s="6"/>
+      <x:c r="Z4" s="6"/>
+      <x:c r="AA4" s="6"/>
+      <x:c r="AB4" s="6"/>
+      <x:c r="AC4" s="6"/>
+      <x:c r="AD4" s="6"/>
+      <x:c r="AE4" s="6"/>
     </x:row>
     <x:row r="5" ht="16.5">
       <x:c r="A5" s="1" t="s">
@@ -1478,6 +1674,14 @@
       <x:c r="U5" s="6"/>
       <x:c r="V5" s="6"/>
       <x:c r="W5" s="6"/>
+      <x:c r="X5" s="6"/>
+      <x:c r="Y5" s="6"/>
+      <x:c r="Z5" s="6"/>
+      <x:c r="AA5" s="6"/>
+      <x:c r="AB5" s="6"/>
+      <x:c r="AC5" s="6"/>
+      <x:c r="AD5" s="6"/>
+      <x:c r="AE5" s="6"/>
     </x:row>
     <x:row r="6" ht="16.5">
       <x:c r="A6" s="2" t="s">
@@ -1519,6 +1723,14 @@
       <x:c r="U6" s="7"/>
       <x:c r="V6" s="7"/>
       <x:c r="W6" s="7"/>
+      <x:c r="X6" s="7"/>
+      <x:c r="Y6" s="7"/>
+      <x:c r="Z6" s="7"/>
+      <x:c r="AA6" s="7"/>
+      <x:c r="AB6" s="7"/>
+      <x:c r="AC6" s="7"/>
+      <x:c r="AD6" s="7"/>
+      <x:c r="AE6" s="7"/>
     </x:row>
     <x:row r="7" ht="16.5">
       <x:c r="A7" s="4"/>
@@ -1562,30 +1774,56 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O7" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/water_cluster_7</x:v>
       </x:c>
       <x:c r="P7" s="4" t="str">
         <x:v>低于地面</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
-        <x:v>-5,-15</x:v>
+        <x:v>-3,-5,-3,-3,-2,-6,-2,-4,-2,-2,-1,-5,-1,-3</x:v>
       </x:c>
       <x:c r="R7" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="S7" s="4" t="n">
-        <x:v>-15</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="T7" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U7" s="9" t="str">
-        <x:v>scene/battle/appearance/Ground_Blue</x:v>
+        <x:v>scene/battle/ground/ground</x:v>
       </x:c>
       <x:c r="V7" s="9" t="str">
-        <x:v>scene/battle/appearance/Ground_Red</x:v>
-      </x:c>
-      <x:c r="W7" s="9"/>
+        <x:v>scene/battle/ground/ground_grid</x:v>
+      </x:c>
+      <x:c r="W7" s="9" t="str">
+        <x:v>scene/battle/ground1001</x:v>
+      </x:c>
+      <x:c r="X7" s="9" t="str">
+        <x:v>0,0</x:v>
+      </x:c>
+      <x:c r="Y7" s="9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z7" s="9" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="AA7" s="9" t="str">
+        <x:v>#B84A33</x:v>
+      </x:c>
+      <x:c r="AB7" s="9" t="str">
+        <x:v>#4A84B8</x:v>
+      </x:c>
+      <x:c r="AC7" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD7" s="9" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="AE7" s="9" t="n">
+        <x:v>0.99</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="16.5">
       <x:c r="A8" s="4"/>
@@ -1605,26 +1843,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O8" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/water_single</x:v>
       </x:c>
       <x:c r="P8" s="4" t="str">
         <x:v>低于地面</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
-        <x:v>-5,-13</x:v>
+        <x:v>-3,9</x:v>
       </x:c>
       <x:c r="R8" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="S8" s="4" t="n">
-        <x:v>-13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="T8" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U8" s="9"/>
       <x:c r="V8" s="9"/>
       <x:c r="W8" s="9"/>
+      <x:c r="X8" s="9"/>
+      <x:c r="Y8" s="9"/>
+      <x:c r="Z8" s="9"/>
+      <x:c r="AA8" s="9"/>
+      <x:c r="AB8" s="9"/>
+      <x:c r="AC8" s="9"/>
+      <x:c r="AD8" s="9"/>
+      <x:c r="AE8" s="9"/>
     </x:row>
     <x:row r="9" ht="16.5">
       <x:c r="A9" s="4"/>
@@ -1644,26 +1890,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O9" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/water_single</x:v>
       </x:c>
       <x:c r="P9" s="4" t="str">
         <x:v>低于地面</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="str">
-        <x:v>-5,-11</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="R9" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S9" s="4" t="n">
-        <x:v>-11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T9" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U9" s="9"/>
       <x:c r="V9" s="9"/>
       <x:c r="W9" s="9"/>
+      <x:c r="X9" s="9"/>
+      <x:c r="Y9" s="9"/>
+      <x:c r="Z9" s="9"/>
+      <x:c r="AA9" s="9"/>
+      <x:c r="AB9" s="9"/>
+      <x:c r="AC9" s="9"/>
+      <x:c r="AD9" s="9"/>
+      <x:c r="AE9" s="9"/>
     </x:row>
     <x:row r="10" ht="16.5">
       <x:c r="A10" s="4"/>
@@ -1683,26 +1937,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O10" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/water_cluster_7</x:v>
       </x:c>
       <x:c r="P10" s="4" t="str">
         <x:v>低于地面</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
-        <x:v>-5,-9</x:v>
+        <x:v>1,3,1,5,2,2,2,4,2,6,3,3,3,5</x:v>
       </x:c>
       <x:c r="R10" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S10" s="4" t="n">
-        <x:v>-9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T10" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U10" s="9"/>
       <x:c r="V10" s="9"/>
       <x:c r="W10" s="9"/>
+      <x:c r="X10" s="9"/>
+      <x:c r="Y10" s="9"/>
+      <x:c r="Z10" s="9"/>
+      <x:c r="AA10" s="9"/>
+      <x:c r="AB10" s="9"/>
+      <x:c r="AC10" s="9"/>
+      <x:c r="AD10" s="9"/>
+      <x:c r="AE10" s="9"/>
     </x:row>
     <x:row r="11" ht="16.5">
       <x:c r="A11" s="4"/>
@@ -1722,26 +1984,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O11" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/water_single</x:v>
       </x:c>
       <x:c r="P11" s="4" t="str">
         <x:v>低于地面</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
-        <x:v>-5,-7</x:v>
+        <x:v>3,-9</x:v>
       </x:c>
       <x:c r="R11" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S11" s="4" t="n">
-        <x:v>-7</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="T11" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U11" s="9"/>
       <x:c r="V11" s="9"/>
       <x:c r="W11" s="9"/>
+      <x:c r="X11" s="9"/>
+      <x:c r="Y11" s="9"/>
+      <x:c r="Z11" s="9"/>
+      <x:c r="AA11" s="9"/>
+      <x:c r="AB11" s="9"/>
+      <x:c r="AC11" s="9"/>
+      <x:c r="AD11" s="9"/>
+      <x:c r="AE11" s="9"/>
     </x:row>
     <x:row r="12" ht="16.5">
       <x:c r="A12" s="4"/>
@@ -1761,26 +2031,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O12" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P12" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
-        <x:v>-5,-5</x:v>
+        <x:v>-4,-10</x:v>
       </x:c>
       <x:c r="R12" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="S12" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="T12" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U12" s="9"/>
       <x:c r="V12" s="9"/>
       <x:c r="W12" s="9"/>
+      <x:c r="X12" s="9"/>
+      <x:c r="Y12" s="9"/>
+      <x:c r="Z12" s="9"/>
+      <x:c r="AA12" s="9"/>
+      <x:c r="AB12" s="9"/>
+      <x:c r="AC12" s="9"/>
+      <x:c r="AD12" s="9"/>
+      <x:c r="AE12" s="9"/>
     </x:row>
     <x:row r="13" ht="16.5">
       <x:c r="A13" s="4"/>
@@ -1800,26 +2078,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O13" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P13" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
-        <x:v>-5,-3</x:v>
+        <x:v>-4,4</x:v>
       </x:c>
       <x:c r="R13" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="S13" s="4" t="n">
-        <x:v>-3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T13" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U13" s="9"/>
       <x:c r="V13" s="9"/>
       <x:c r="W13" s="9"/>
+      <x:c r="X13" s="9"/>
+      <x:c r="Y13" s="9"/>
+      <x:c r="Z13" s="9"/>
+      <x:c r="AA13" s="9"/>
+      <x:c r="AB13" s="9"/>
+      <x:c r="AC13" s="9"/>
+      <x:c r="AD13" s="9"/>
+      <x:c r="AE13" s="9"/>
     </x:row>
     <x:row r="14" ht="16.5">
       <x:c r="A14" s="4"/>
@@ -1839,26 +2125,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O14" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P14" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
-        <x:v>-5,-1</x:v>
+        <x:v>-2,10</x:v>
       </x:c>
       <x:c r="R14" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="S14" s="4" t="n">
-        <x:v>-1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="T14" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U14" s="9"/>
       <x:c r="V14" s="9"/>
       <x:c r="W14" s="9"/>
+      <x:c r="X14" s="9"/>
+      <x:c r="Y14" s="9"/>
+      <x:c r="Z14" s="9"/>
+      <x:c r="AA14" s="9"/>
+      <x:c r="AB14" s="9"/>
+      <x:c r="AC14" s="9"/>
+      <x:c r="AD14" s="9"/>
+      <x:c r="AE14" s="9"/>
     </x:row>
     <x:row r="15" ht="16.5">
       <x:c r="A15" s="4"/>
@@ -1878,26 +2172,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O15" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P15" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
-        <x:v>-5,1</x:v>
+        <x:v>0,-6</x:v>
       </x:c>
       <x:c r="R15" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S15" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="T15" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U15" s="9"/>
       <x:c r="V15" s="9"/>
       <x:c r="W15" s="9"/>
+      <x:c r="X15" s="9"/>
+      <x:c r="Y15" s="9"/>
+      <x:c r="Z15" s="9"/>
+      <x:c r="AA15" s="9"/>
+      <x:c r="AB15" s="9"/>
+      <x:c r="AC15" s="9"/>
+      <x:c r="AD15" s="9"/>
+      <x:c r="AE15" s="9"/>
     </x:row>
     <x:row r="16" ht="16.5">
       <x:c r="A16" s="4"/>
@@ -1917,26 +2219,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O16" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P16" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>-5,3</x:v>
+        <x:v>0,6</x:v>
       </x:c>
       <x:c r="R16" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S16" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="T16" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U16" s="9"/>
       <x:c r="V16" s="9"/>
       <x:c r="W16" s="9"/>
+      <x:c r="X16" s="9"/>
+      <x:c r="Y16" s="9"/>
+      <x:c r="Z16" s="9"/>
+      <x:c r="AA16" s="9"/>
+      <x:c r="AB16" s="9"/>
+      <x:c r="AC16" s="9"/>
+      <x:c r="AD16" s="9"/>
+      <x:c r="AE16" s="9"/>
     </x:row>
     <x:row r="17" ht="16.5">
       <x:c r="A17" s="4"/>
@@ -1956,26 +2266,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O17" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P17" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>-5,5</x:v>
+        <x:v>2,-10</x:v>
       </x:c>
       <x:c r="R17" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S17" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="T17" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U17" s="9"/>
       <x:c r="V17" s="9"/>
       <x:c r="W17" s="9"/>
+      <x:c r="X17" s="9"/>
+      <x:c r="Y17" s="9"/>
+      <x:c r="Z17" s="9"/>
+      <x:c r="AA17" s="9"/>
+      <x:c r="AB17" s="9"/>
+      <x:c r="AC17" s="9"/>
+      <x:c r="AD17" s="9"/>
+      <x:c r="AE17" s="9"/>
     </x:row>
     <x:row r="18" ht="16.5">
       <x:c r="A18" s="4"/>
@@ -1995,26 +2313,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O18" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P18" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
-        <x:v>-5,7</x:v>
+        <x:v>4,-4</x:v>
       </x:c>
       <x:c r="R18" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S18" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="T18" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U18" s="9"/>
       <x:c r="V18" s="9"/>
       <x:c r="W18" s="9"/>
+      <x:c r="X18" s="9"/>
+      <x:c r="Y18" s="9"/>
+      <x:c r="Z18" s="9"/>
+      <x:c r="AA18" s="9"/>
+      <x:c r="AB18" s="9"/>
+      <x:c r="AC18" s="9"/>
+      <x:c r="AD18" s="9"/>
+      <x:c r="AE18" s="9"/>
     </x:row>
     <x:row r="19" ht="16.5">
       <x:c r="A19" s="4"/>
@@ -2034,26 +2360,34 @@
         <x:v>静态图片</x:v>
       </x:c>
       <x:c r="O19" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
+        <x:v>scene/battle/ground/mountain</x:v>
       </x:c>
       <x:c r="P19" s="4" t="str">
-        <x:v>低于地面</x:v>
+        <x:v>高于地面</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>-5,9</x:v>
+        <x:v>4,10</x:v>
       </x:c>
       <x:c r="R19" s="4" t="n">
-        <x:v>-5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S19" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="T19" s="4" t="str">
-        <x:v>0.25,0</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="U19" s="9"/>
       <x:c r="V19" s="9"/>
       <x:c r="W19" s="9"/>
+      <x:c r="X19" s="9"/>
+      <x:c r="Y19" s="9"/>
+      <x:c r="Z19" s="9"/>
+      <x:c r="AA19" s="9"/>
+      <x:c r="AB19" s="9"/>
+      <x:c r="AC19" s="9"/>
+      <x:c r="AD19" s="9"/>
+      <x:c r="AE19" s="9"/>
     </x:row>
     <x:row r="20" ht="16.5">
       <x:c r="A20" s="4"/>
@@ -2069,27 +2403,13 @@
       <x:c r="K20" s="4"/>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="4"/>
-      <x:c r="N20" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O20" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P20" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q20" s="4" t="str">
-        <x:v>-5,11</x:v>
-      </x:c>
-      <x:c r="R20" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S20" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T20" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N20" s="4"/>
+      <x:c r="O20" s="5"/>
+      <x:c r="P20" s="4"/>
+      <x:c r="Q20" s="4"/>
+      <x:c r="R20" s="4"/>
+      <x:c r="S20" s="4"/>
+      <x:c r="T20" s="4"/>
       <x:c r="U20" s="9"/>
       <x:c r="V20" s="9"/>
       <x:c r="W20" s="9"/>
@@ -2108,27 +2428,13 @@
       <x:c r="K21" s="4"/>
       <x:c r="L21" s="4"/>
       <x:c r="M21" s="4"/>
-      <x:c r="N21" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O21" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P21" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q21" s="4" t="str">
-        <x:v>-5,13</x:v>
-      </x:c>
-      <x:c r="R21" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S21" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T21" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N21" s="4"/>
+      <x:c r="O21" s="5"/>
+      <x:c r="P21" s="4"/>
+      <x:c r="Q21" s="4"/>
+      <x:c r="R21" s="4"/>
+      <x:c r="S21" s="4"/>
+      <x:c r="T21" s="4"/>
       <x:c r="U21" s="9"/>
       <x:c r="V21" s="9"/>
       <x:c r="W21" s="9"/>
@@ -2147,27 +2453,13 @@
       <x:c r="K22" s="4"/>
       <x:c r="L22" s="4"/>
       <x:c r="M22" s="4"/>
-      <x:c r="N22" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O22" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P22" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q22" s="4" t="str">
-        <x:v>-5,15</x:v>
-      </x:c>
-      <x:c r="R22" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S22" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T22" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N22" s="4"/>
+      <x:c r="O22" s="5"/>
+      <x:c r="P22" s="4"/>
+      <x:c r="Q22" s="4"/>
+      <x:c r="R22" s="4"/>
+      <x:c r="S22" s="4"/>
+      <x:c r="T22" s="4"/>
       <x:c r="U22" s="9"/>
       <x:c r="V22" s="9"/>
       <x:c r="W22" s="9"/>
@@ -2186,27 +2478,13 @@
       <x:c r="K23" s="4"/>
       <x:c r="L23" s="4"/>
       <x:c r="M23" s="4"/>
-      <x:c r="N23" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O23" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P23" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q23" s="4" t="str">
-        <x:v>-4,-14</x:v>
-      </x:c>
-      <x:c r="R23" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S23" s="4" t="n">
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="T23" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N23" s="4"/>
+      <x:c r="O23" s="5"/>
+      <x:c r="P23" s="4"/>
+      <x:c r="Q23" s="4"/>
+      <x:c r="R23" s="4"/>
+      <x:c r="S23" s="4"/>
+      <x:c r="T23" s="4"/>
       <x:c r="U23" s="9"/>
       <x:c r="V23" s="9"/>
       <x:c r="W23" s="9"/>
@@ -2225,27 +2503,13 @@
       <x:c r="K24" s="4"/>
       <x:c r="L24" s="4"/>
       <x:c r="M24" s="4"/>
-      <x:c r="N24" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O24" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P24" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q24" s="4" t="str">
-        <x:v>-4,-12</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S24" s="4" t="n">
-        <x:v>-12</x:v>
-      </x:c>
-      <x:c r="T24" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N24" s="4"/>
+      <x:c r="O24" s="5"/>
+      <x:c r="P24" s="4"/>
+      <x:c r="Q24" s="4"/>
+      <x:c r="R24" s="4"/>
+      <x:c r="S24" s="4"/>
+      <x:c r="T24" s="4"/>
       <x:c r="U24" s="9"/>
       <x:c r="V24" s="9"/>
       <x:c r="W24" s="9"/>
@@ -2264,27 +2528,13 @@
       <x:c r="K25" s="4"/>
       <x:c r="L25" s="4"/>
       <x:c r="M25" s="4"/>
-      <x:c r="N25" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O25" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P25" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q25" s="4" t="str">
-        <x:v>-4,-10</x:v>
-      </x:c>
-      <x:c r="R25" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S25" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T25" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N25" s="4"/>
+      <x:c r="O25" s="5"/>
+      <x:c r="P25" s="4"/>
+      <x:c r="Q25" s="4"/>
+      <x:c r="R25" s="4"/>
+      <x:c r="S25" s="4"/>
+      <x:c r="T25" s="4"/>
       <x:c r="U25" s="9"/>
       <x:c r="V25" s="9"/>
       <x:c r="W25" s="9"/>
@@ -2303,27 +2553,13 @@
       <x:c r="K26" s="4"/>
       <x:c r="L26" s="4"/>
       <x:c r="M26" s="4"/>
-      <x:c r="N26" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O26" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P26" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q26" s="4" t="str">
-        <x:v>-4,-8</x:v>
-      </x:c>
-      <x:c r="R26" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S26" s="4" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="T26" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N26" s="4"/>
+      <x:c r="O26" s="5"/>
+      <x:c r="P26" s="4"/>
+      <x:c r="Q26" s="4"/>
+      <x:c r="R26" s="4"/>
+      <x:c r="S26" s="4"/>
+      <x:c r="T26" s="4"/>
       <x:c r="U26" s="9"/>
       <x:c r="V26" s="9"/>
       <x:c r="W26" s="9"/>
@@ -2342,27 +2578,13 @@
       <x:c r="K27" s="4"/>
       <x:c r="L27" s="4"/>
       <x:c r="M27" s="4"/>
-      <x:c r="N27" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O27" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P27" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q27" s="4" t="str">
-        <x:v>-4,-6</x:v>
-      </x:c>
-      <x:c r="R27" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S27" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T27" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N27" s="4"/>
+      <x:c r="O27" s="5"/>
+      <x:c r="P27" s="4"/>
+      <x:c r="Q27" s="4"/>
+      <x:c r="R27" s="4"/>
+      <x:c r="S27" s="4"/>
+      <x:c r="T27" s="4"/>
       <x:c r="U27" s="9"/>
       <x:c r="V27" s="9"/>
       <x:c r="W27" s="9"/>
@@ -2381,27 +2603,13 @@
       <x:c r="K28" s="4"/>
       <x:c r="L28" s="4"/>
       <x:c r="M28" s="4"/>
-      <x:c r="N28" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O28" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P28" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q28" s="4" t="str">
-        <x:v>-4,-4</x:v>
-      </x:c>
-      <x:c r="R28" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S28" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T28" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N28" s="4"/>
+      <x:c r="O28" s="5"/>
+      <x:c r="P28" s="4"/>
+      <x:c r="Q28" s="4"/>
+      <x:c r="R28" s="4"/>
+      <x:c r="S28" s="4"/>
+      <x:c r="T28" s="4"/>
       <x:c r="U28" s="9"/>
       <x:c r="V28" s="9"/>
       <x:c r="W28" s="9"/>
@@ -2420,27 +2628,13 @@
       <x:c r="K29" s="4"/>
       <x:c r="L29" s="4"/>
       <x:c r="M29" s="4"/>
-      <x:c r="N29" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O29" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P29" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q29" s="4" t="str">
-        <x:v>-4,-2</x:v>
-      </x:c>
-      <x:c r="R29" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S29" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="T29" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N29" s="4"/>
+      <x:c r="O29" s="5"/>
+      <x:c r="P29" s="4"/>
+      <x:c r="Q29" s="4"/>
+      <x:c r="R29" s="4"/>
+      <x:c r="S29" s="4"/>
+      <x:c r="T29" s="4"/>
       <x:c r="U29" s="9"/>
       <x:c r="V29" s="9"/>
       <x:c r="W29" s="9"/>
@@ -2459,27 +2653,13 @@
       <x:c r="K30" s="4"/>
       <x:c r="L30" s="4"/>
       <x:c r="M30" s="4"/>
-      <x:c r="N30" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O30" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P30" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q30" s="4" t="str">
-        <x:v>-4,0</x:v>
-      </x:c>
-      <x:c r="R30" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S30" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T30" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N30" s="4"/>
+      <x:c r="O30" s="5"/>
+      <x:c r="P30" s="4"/>
+      <x:c r="Q30" s="4"/>
+      <x:c r="R30" s="4"/>
+      <x:c r="S30" s="4"/>
+      <x:c r="T30" s="4"/>
       <x:c r="U30" s="9"/>
       <x:c r="V30" s="9"/>
       <x:c r="W30" s="9"/>
@@ -2498,27 +2678,13 @@
       <x:c r="K31" s="4"/>
       <x:c r="L31" s="4"/>
       <x:c r="M31" s="4"/>
-      <x:c r="N31" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O31" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P31" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q31" s="4" t="str">
-        <x:v>-4,2</x:v>
-      </x:c>
-      <x:c r="R31" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S31" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T31" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N31" s="4"/>
+      <x:c r="O31" s="5"/>
+      <x:c r="P31" s="4"/>
+      <x:c r="Q31" s="4"/>
+      <x:c r="R31" s="4"/>
+      <x:c r="S31" s="4"/>
+      <x:c r="T31" s="4"/>
       <x:c r="U31" s="9"/>
       <x:c r="V31" s="9"/>
       <x:c r="W31" s="9"/>
@@ -2537,27 +2703,13 @@
       <x:c r="K32" s="4"/>
       <x:c r="L32" s="4"/>
       <x:c r="M32" s="4"/>
-      <x:c r="N32" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O32" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P32" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q32" s="4" t="str">
-        <x:v>-4,4</x:v>
-      </x:c>
-      <x:c r="R32" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S32" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T32" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N32" s="4"/>
+      <x:c r="O32" s="5"/>
+      <x:c r="P32" s="4"/>
+      <x:c r="Q32" s="4"/>
+      <x:c r="R32" s="4"/>
+      <x:c r="S32" s="4"/>
+      <x:c r="T32" s="4"/>
       <x:c r="U32" s="9"/>
       <x:c r="V32" s="9"/>
       <x:c r="W32" s="9"/>
@@ -2576,27 +2728,13 @@
       <x:c r="K33" s="4"/>
       <x:c r="L33" s="4"/>
       <x:c r="M33" s="4"/>
-      <x:c r="N33" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O33" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P33" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q33" s="4" t="str">
-        <x:v>-4,6</x:v>
-      </x:c>
-      <x:c r="R33" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S33" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T33" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N33" s="4"/>
+      <x:c r="O33" s="5"/>
+      <x:c r="P33" s="4"/>
+      <x:c r="Q33" s="4"/>
+      <x:c r="R33" s="4"/>
+      <x:c r="S33" s="4"/>
+      <x:c r="T33" s="4"/>
       <x:c r="U33" s="9"/>
       <x:c r="V33" s="9"/>
       <x:c r="W33" s="9"/>
@@ -2615,27 +2753,13 @@
       <x:c r="K34" s="4"/>
       <x:c r="L34" s="4"/>
       <x:c r="M34" s="4"/>
-      <x:c r="N34" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O34" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P34" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q34" s="4" t="str">
-        <x:v>-4,8</x:v>
-      </x:c>
-      <x:c r="R34" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S34" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T34" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N34" s="4"/>
+      <x:c r="O34" s="5"/>
+      <x:c r="P34" s="4"/>
+      <x:c r="Q34" s="4"/>
+      <x:c r="R34" s="4"/>
+      <x:c r="S34" s="4"/>
+      <x:c r="T34" s="4"/>
       <x:c r="U34" s="9"/>
       <x:c r="V34" s="9"/>
       <x:c r="W34" s="9"/>
@@ -2654,27 +2778,13 @@
       <x:c r="K35" s="4"/>
       <x:c r="L35" s="4"/>
       <x:c r="M35" s="4"/>
-      <x:c r="N35" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O35" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P35" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q35" s="4" t="str">
-        <x:v>-4,10</x:v>
-      </x:c>
-      <x:c r="R35" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S35" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T35" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N35" s="4"/>
+      <x:c r="O35" s="5"/>
+      <x:c r="P35" s="4"/>
+      <x:c r="Q35" s="4"/>
+      <x:c r="R35" s="4"/>
+      <x:c r="S35" s="4"/>
+      <x:c r="T35" s="4"/>
       <x:c r="U35" s="9"/>
       <x:c r="V35" s="9"/>
       <x:c r="W35" s="9"/>
@@ -2693,27 +2803,13 @@
       <x:c r="K36" s="4"/>
       <x:c r="L36" s="4"/>
       <x:c r="M36" s="4"/>
-      <x:c r="N36" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O36" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P36" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q36" s="4" t="str">
-        <x:v>-4,12</x:v>
-      </x:c>
-      <x:c r="R36" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S36" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T36" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N36" s="4"/>
+      <x:c r="O36" s="5"/>
+      <x:c r="P36" s="4"/>
+      <x:c r="Q36" s="4"/>
+      <x:c r="R36" s="4"/>
+      <x:c r="S36" s="4"/>
+      <x:c r="T36" s="4"/>
       <x:c r="U36" s="9"/>
       <x:c r="V36" s="9"/>
       <x:c r="W36" s="9"/>
@@ -2732,27 +2828,13 @@
       <x:c r="K37" s="4"/>
       <x:c r="L37" s="4"/>
       <x:c r="M37" s="4"/>
-      <x:c r="N37" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O37" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P37" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q37" s="4" t="str">
-        <x:v>-4,14</x:v>
-      </x:c>
-      <x:c r="R37" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S37" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T37" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N37" s="4"/>
+      <x:c r="O37" s="5"/>
+      <x:c r="P37" s="4"/>
+      <x:c r="Q37" s="4"/>
+      <x:c r="R37" s="4"/>
+      <x:c r="S37" s="4"/>
+      <x:c r="T37" s="4"/>
       <x:c r="U37" s="9"/>
       <x:c r="V37" s="9"/>
       <x:c r="W37" s="9"/>
@@ -2771,27 +2853,13 @@
       <x:c r="K38" s="4"/>
       <x:c r="L38" s="4"/>
       <x:c r="M38" s="4"/>
-      <x:c r="N38" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O38" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P38" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q38" s="4" t="str">
-        <x:v>-3,-15</x:v>
-      </x:c>
-      <x:c r="R38" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S38" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T38" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N38" s="4"/>
+      <x:c r="O38" s="5"/>
+      <x:c r="P38" s="4"/>
+      <x:c r="Q38" s="4"/>
+      <x:c r="R38" s="4"/>
+      <x:c r="S38" s="4"/>
+      <x:c r="T38" s="4"/>
       <x:c r="U38" s="9"/>
       <x:c r="V38" s="9"/>
       <x:c r="W38" s="9"/>
@@ -2810,27 +2878,13 @@
       <x:c r="K39" s="4"/>
       <x:c r="L39" s="4"/>
       <x:c r="M39" s="4"/>
-      <x:c r="N39" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O39" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P39" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q39" s="4" t="str">
-        <x:v>-3,-13</x:v>
-      </x:c>
-      <x:c r="R39" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S39" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T39" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N39" s="4"/>
+      <x:c r="O39" s="5"/>
+      <x:c r="P39" s="4"/>
+      <x:c r="Q39" s="4"/>
+      <x:c r="R39" s="4"/>
+      <x:c r="S39" s="4"/>
+      <x:c r="T39" s="4"/>
       <x:c r="U39" s="9"/>
       <x:c r="V39" s="9"/>
       <x:c r="W39" s="9"/>
@@ -2849,27 +2903,13 @@
       <x:c r="K40" s="4"/>
       <x:c r="L40" s="4"/>
       <x:c r="M40" s="4"/>
-      <x:c r="N40" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O40" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P40" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q40" s="4" t="str">
-        <x:v>-3,-11</x:v>
-      </x:c>
-      <x:c r="R40" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S40" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T40" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N40" s="4"/>
+      <x:c r="O40" s="5"/>
+      <x:c r="P40" s="4"/>
+      <x:c r="Q40" s="4"/>
+      <x:c r="R40" s="4"/>
+      <x:c r="S40" s="4"/>
+      <x:c r="T40" s="4"/>
       <x:c r="U40" s="9"/>
       <x:c r="V40" s="9"/>
       <x:c r="W40" s="9"/>
@@ -2888,27 +2928,13 @@
       <x:c r="K41" s="4"/>
       <x:c r="L41" s="4"/>
       <x:c r="M41" s="4"/>
-      <x:c r="N41" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O41" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P41" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q41" s="4" t="str">
-        <x:v>-3,-9</x:v>
-      </x:c>
-      <x:c r="R41" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S41" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T41" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N41" s="4"/>
+      <x:c r="O41" s="5"/>
+      <x:c r="P41" s="4"/>
+      <x:c r="Q41" s="4"/>
+      <x:c r="R41" s="4"/>
+      <x:c r="S41" s="4"/>
+      <x:c r="T41" s="4"/>
       <x:c r="U41" s="9"/>
       <x:c r="V41" s="9"/>
       <x:c r="W41" s="9"/>
@@ -2927,27 +2953,13 @@
       <x:c r="K42" s="4"/>
       <x:c r="L42" s="4"/>
       <x:c r="M42" s="4"/>
-      <x:c r="N42" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O42" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P42" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q42" s="4" t="str">
-        <x:v>-3,-7</x:v>
-      </x:c>
-      <x:c r="R42" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S42" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T42" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N42" s="4"/>
+      <x:c r="O42" s="5"/>
+      <x:c r="P42" s="4"/>
+      <x:c r="Q42" s="4"/>
+      <x:c r="R42" s="4"/>
+      <x:c r="S42" s="4"/>
+      <x:c r="T42" s="4"/>
       <x:c r="U42" s="9"/>
       <x:c r="V42" s="9"/>
       <x:c r="W42" s="9"/>
@@ -2966,27 +2978,13 @@
       <x:c r="K43" s="4"/>
       <x:c r="L43" s="4"/>
       <x:c r="M43" s="4"/>
-      <x:c r="N43" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O43" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P43" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q43" s="4" t="str">
-        <x:v>-3,-5</x:v>
-      </x:c>
-      <x:c r="R43" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S43" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T43" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N43" s="4"/>
+      <x:c r="O43" s="5"/>
+      <x:c r="P43" s="4"/>
+      <x:c r="Q43" s="4"/>
+      <x:c r="R43" s="4"/>
+      <x:c r="S43" s="4"/>
+      <x:c r="T43" s="4"/>
       <x:c r="U43" s="9"/>
       <x:c r="V43" s="9"/>
       <x:c r="W43" s="9"/>
@@ -3005,27 +3003,13 @@
       <x:c r="K44" s="4"/>
       <x:c r="L44" s="4"/>
       <x:c r="M44" s="4"/>
-      <x:c r="N44" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O44" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P44" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q44" s="4" t="str">
-        <x:v>-3,-3</x:v>
-      </x:c>
-      <x:c r="R44" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S44" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T44" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N44" s="4"/>
+      <x:c r="O44" s="5"/>
+      <x:c r="P44" s="4"/>
+      <x:c r="Q44" s="4"/>
+      <x:c r="R44" s="4"/>
+      <x:c r="S44" s="4"/>
+      <x:c r="T44" s="4"/>
       <x:c r="U44" s="9"/>
       <x:c r="V44" s="9"/>
       <x:c r="W44" s="9"/>
@@ -3044,27 +3028,13 @@
       <x:c r="K45" s="4"/>
       <x:c r="L45" s="4"/>
       <x:c r="M45" s="4"/>
-      <x:c r="N45" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O45" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P45" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q45" s="4" t="str">
-        <x:v>-3,-1</x:v>
-      </x:c>
-      <x:c r="R45" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S45" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T45" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N45" s="4"/>
+      <x:c r="O45" s="5"/>
+      <x:c r="P45" s="4"/>
+      <x:c r="Q45" s="4"/>
+      <x:c r="R45" s="4"/>
+      <x:c r="S45" s="4"/>
+      <x:c r="T45" s="4"/>
       <x:c r="U45" s="9"/>
       <x:c r="V45" s="9"/>
       <x:c r="W45" s="9"/>
@@ -3083,27 +3053,13 @@
       <x:c r="K46" s="4"/>
       <x:c r="L46" s="4"/>
       <x:c r="M46" s="4"/>
-      <x:c r="N46" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O46" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P46" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q46" s="4" t="str">
-        <x:v>-3,1</x:v>
-      </x:c>
-      <x:c r="R46" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S46" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T46" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N46" s="4"/>
+      <x:c r="O46" s="5"/>
+      <x:c r="P46" s="4"/>
+      <x:c r="Q46" s="4"/>
+      <x:c r="R46" s="4"/>
+      <x:c r="S46" s="4"/>
+      <x:c r="T46" s="4"/>
       <x:c r="U46" s="9"/>
       <x:c r="V46" s="9"/>
       <x:c r="W46" s="9"/>
@@ -3122,27 +3078,13 @@
       <x:c r="K47" s="4"/>
       <x:c r="L47" s="4"/>
       <x:c r="M47" s="4"/>
-      <x:c r="N47" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O47" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P47" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q47" s="4" t="str">
-        <x:v>-3,3</x:v>
-      </x:c>
-      <x:c r="R47" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S47" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T47" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N47" s="4"/>
+      <x:c r="O47" s="5"/>
+      <x:c r="P47" s="4"/>
+      <x:c r="Q47" s="4"/>
+      <x:c r="R47" s="4"/>
+      <x:c r="S47" s="4"/>
+      <x:c r="T47" s="4"/>
       <x:c r="U47" s="9"/>
       <x:c r="V47" s="9"/>
       <x:c r="W47" s="9"/>
@@ -3161,27 +3103,13 @@
       <x:c r="K48" s="4"/>
       <x:c r="L48" s="4"/>
       <x:c r="M48" s="4"/>
-      <x:c r="N48" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O48" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P48" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q48" s="4" t="str">
-        <x:v>-3,5</x:v>
-      </x:c>
-      <x:c r="R48" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S48" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T48" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N48" s="4"/>
+      <x:c r="O48" s="5"/>
+      <x:c r="P48" s="4"/>
+      <x:c r="Q48" s="4"/>
+      <x:c r="R48" s="4"/>
+      <x:c r="S48" s="4"/>
+      <x:c r="T48" s="4"/>
       <x:c r="U48" s="9"/>
       <x:c r="V48" s="9"/>
       <x:c r="W48" s="9"/>
@@ -3200,27 +3128,13 @@
       <x:c r="K49" s="4"/>
       <x:c r="L49" s="4"/>
       <x:c r="M49" s="4"/>
-      <x:c r="N49" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O49" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P49" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q49" s="4" t="str">
-        <x:v>-3,7</x:v>
-      </x:c>
-      <x:c r="R49" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S49" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T49" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N49" s="4"/>
+      <x:c r="O49" s="5"/>
+      <x:c r="P49" s="4"/>
+      <x:c r="Q49" s="4"/>
+      <x:c r="R49" s="4"/>
+      <x:c r="S49" s="4"/>
+      <x:c r="T49" s="4"/>
       <x:c r="U49" s="9"/>
       <x:c r="V49" s="9"/>
       <x:c r="W49" s="9"/>
@@ -3239,27 +3153,13 @@
       <x:c r="K50" s="4"/>
       <x:c r="L50" s="4"/>
       <x:c r="M50" s="4"/>
-      <x:c r="N50" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O50" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P50" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q50" s="4" t="str">
-        <x:v>-3,9</x:v>
-      </x:c>
-      <x:c r="R50" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S50" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T50" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N50" s="4"/>
+      <x:c r="O50" s="5"/>
+      <x:c r="P50" s="4"/>
+      <x:c r="Q50" s="4"/>
+      <x:c r="R50" s="4"/>
+      <x:c r="S50" s="4"/>
+      <x:c r="T50" s="4"/>
       <x:c r="U50" s="9"/>
       <x:c r="V50" s="9"/>
       <x:c r="W50" s="9"/>
@@ -3278,27 +3178,13 @@
       <x:c r="K51" s="4"/>
       <x:c r="L51" s="4"/>
       <x:c r="M51" s="4"/>
-      <x:c r="N51" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O51" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P51" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q51" s="4" t="str">
-        <x:v>-3,11</x:v>
-      </x:c>
-      <x:c r="R51" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S51" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T51" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N51" s="4"/>
+      <x:c r="O51" s="5"/>
+      <x:c r="P51" s="4"/>
+      <x:c r="Q51" s="4"/>
+      <x:c r="R51" s="4"/>
+      <x:c r="S51" s="4"/>
+      <x:c r="T51" s="4"/>
       <x:c r="U51" s="9"/>
       <x:c r="V51" s="9"/>
       <x:c r="W51" s="9"/>
@@ -3317,27 +3203,13 @@
       <x:c r="K52" s="4"/>
       <x:c r="L52" s="4"/>
       <x:c r="M52" s="4"/>
-      <x:c r="N52" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O52" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P52" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q52" s="4" t="str">
-        <x:v>-3,13</x:v>
-      </x:c>
-      <x:c r="R52" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S52" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T52" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N52" s="4"/>
+      <x:c r="O52" s="5"/>
+      <x:c r="P52" s="4"/>
+      <x:c r="Q52" s="4"/>
+      <x:c r="R52" s="4"/>
+      <x:c r="S52" s="4"/>
+      <x:c r="T52" s="4"/>
       <x:c r="U52" s="9"/>
       <x:c r="V52" s="9"/>
       <x:c r="W52" s="9"/>
@@ -3356,27 +3228,13 @@
       <x:c r="K53" s="4"/>
       <x:c r="L53" s="4"/>
       <x:c r="M53" s="4"/>
-      <x:c r="N53" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O53" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P53" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q53" s="4" t="str">
-        <x:v>-3,15</x:v>
-      </x:c>
-      <x:c r="R53" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S53" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T53" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N53" s="4"/>
+      <x:c r="O53" s="5"/>
+      <x:c r="P53" s="4"/>
+      <x:c r="Q53" s="4"/>
+      <x:c r="R53" s="4"/>
+      <x:c r="S53" s="4"/>
+      <x:c r="T53" s="4"/>
       <x:c r="U53" s="9"/>
       <x:c r="V53" s="9"/>
       <x:c r="W53" s="9"/>
@@ -3395,27 +3253,13 @@
       <x:c r="K54" s="4"/>
       <x:c r="L54" s="4"/>
       <x:c r="M54" s="4"/>
-      <x:c r="N54" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O54" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P54" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q54" s="4" t="str">
-        <x:v>-2,-14</x:v>
-      </x:c>
-      <x:c r="R54" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S54" s="4" t="n">
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="T54" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N54" s="4"/>
+      <x:c r="O54" s="5"/>
+      <x:c r="P54" s="4"/>
+      <x:c r="Q54" s="4"/>
+      <x:c r="R54" s="4"/>
+      <x:c r="S54" s="4"/>
+      <x:c r="T54" s="4"/>
       <x:c r="U54" s="9"/>
       <x:c r="V54" s="9"/>
       <x:c r="W54" s="9"/>
@@ -3434,27 +3278,13 @@
       <x:c r="K55" s="4"/>
       <x:c r="L55" s="4"/>
       <x:c r="M55" s="4"/>
-      <x:c r="N55" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O55" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P55" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q55" s="4" t="str">
-        <x:v>-2,-12</x:v>
-      </x:c>
-      <x:c r="R55" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S55" s="4" t="n">
-        <x:v>-12</x:v>
-      </x:c>
-      <x:c r="T55" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N55" s="4"/>
+      <x:c r="O55" s="5"/>
+      <x:c r="P55" s="4"/>
+      <x:c r="Q55" s="4"/>
+      <x:c r="R55" s="4"/>
+      <x:c r="S55" s="4"/>
+      <x:c r="T55" s="4"/>
       <x:c r="U55" s="9"/>
       <x:c r="V55" s="9"/>
       <x:c r="W55" s="9"/>
@@ -3473,27 +3303,13 @@
       <x:c r="K56" s="4"/>
       <x:c r="L56" s="4"/>
       <x:c r="M56" s="4"/>
-      <x:c r="N56" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O56" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P56" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q56" s="4" t="str">
-        <x:v>-2,-10</x:v>
-      </x:c>
-      <x:c r="R56" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S56" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T56" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N56" s="4"/>
+      <x:c r="O56" s="5"/>
+      <x:c r="P56" s="4"/>
+      <x:c r="Q56" s="4"/>
+      <x:c r="R56" s="4"/>
+      <x:c r="S56" s="4"/>
+      <x:c r="T56" s="4"/>
       <x:c r="U56" s="9"/>
       <x:c r="V56" s="9"/>
       <x:c r="W56" s="9"/>
@@ -3512,27 +3328,13 @@
       <x:c r="K57" s="4"/>
       <x:c r="L57" s="4"/>
       <x:c r="M57" s="4"/>
-      <x:c r="N57" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O57" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P57" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q57" s="4" t="str">
-        <x:v>-2,-8</x:v>
-      </x:c>
-      <x:c r="R57" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S57" s="4" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="T57" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N57" s="4"/>
+      <x:c r="O57" s="5"/>
+      <x:c r="P57" s="4"/>
+      <x:c r="Q57" s="4"/>
+      <x:c r="R57" s="4"/>
+      <x:c r="S57" s="4"/>
+      <x:c r="T57" s="4"/>
       <x:c r="U57" s="9"/>
       <x:c r="V57" s="9"/>
       <x:c r="W57" s="9"/>
@@ -3551,27 +3353,13 @@
       <x:c r="K58" s="4"/>
       <x:c r="L58" s="4"/>
       <x:c r="M58" s="4"/>
-      <x:c r="N58" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O58" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P58" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q58" s="4" t="str">
-        <x:v>-2,-6</x:v>
-      </x:c>
-      <x:c r="R58" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S58" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T58" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N58" s="4"/>
+      <x:c r="O58" s="5"/>
+      <x:c r="P58" s="4"/>
+      <x:c r="Q58" s="4"/>
+      <x:c r="R58" s="4"/>
+      <x:c r="S58" s="4"/>
+      <x:c r="T58" s="4"/>
       <x:c r="U58" s="9"/>
       <x:c r="V58" s="9"/>
       <x:c r="W58" s="9"/>
@@ -3590,27 +3378,13 @@
       <x:c r="K59" s="4"/>
       <x:c r="L59" s="4"/>
       <x:c r="M59" s="4"/>
-      <x:c r="N59" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O59" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P59" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q59" s="4" t="str">
-        <x:v>-2,-4</x:v>
-      </x:c>
-      <x:c r="R59" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S59" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T59" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N59" s="4"/>
+      <x:c r="O59" s="5"/>
+      <x:c r="P59" s="4"/>
+      <x:c r="Q59" s="4"/>
+      <x:c r="R59" s="4"/>
+      <x:c r="S59" s="4"/>
+      <x:c r="T59" s="4"/>
       <x:c r="U59" s="9"/>
       <x:c r="V59" s="9"/>
       <x:c r="W59" s="9"/>
@@ -3629,27 +3403,13 @@
       <x:c r="K60" s="4"/>
       <x:c r="L60" s="4"/>
       <x:c r="M60" s="4"/>
-      <x:c r="N60" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O60" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P60" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q60" s="4" t="str">
-        <x:v>-2,-2</x:v>
-      </x:c>
-      <x:c r="R60" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S60" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="T60" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N60" s="4"/>
+      <x:c r="O60" s="5"/>
+      <x:c r="P60" s="4"/>
+      <x:c r="Q60" s="4"/>
+      <x:c r="R60" s="4"/>
+      <x:c r="S60" s="4"/>
+      <x:c r="T60" s="4"/>
       <x:c r="U60" s="9"/>
       <x:c r="V60" s="9"/>
       <x:c r="W60" s="9"/>
@@ -3668,27 +3428,13 @@
       <x:c r="K61" s="4"/>
       <x:c r="L61" s="4"/>
       <x:c r="M61" s="4"/>
-      <x:c r="N61" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O61" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P61" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q61" s="4" t="str">
-        <x:v>-2,0</x:v>
-      </x:c>
-      <x:c r="R61" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S61" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T61" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N61" s="4"/>
+      <x:c r="O61" s="5"/>
+      <x:c r="P61" s="4"/>
+      <x:c r="Q61" s="4"/>
+      <x:c r="R61" s="4"/>
+      <x:c r="S61" s="4"/>
+      <x:c r="T61" s="4"/>
       <x:c r="U61" s="9"/>
       <x:c r="V61" s="9"/>
       <x:c r="W61" s="9"/>
@@ -3707,27 +3453,13 @@
       <x:c r="K62" s="4"/>
       <x:c r="L62" s="4"/>
       <x:c r="M62" s="4"/>
-      <x:c r="N62" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O62" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P62" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q62" s="4" t="str">
-        <x:v>-2,2</x:v>
-      </x:c>
-      <x:c r="R62" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S62" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T62" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N62" s="4"/>
+      <x:c r="O62" s="5"/>
+      <x:c r="P62" s="4"/>
+      <x:c r="Q62" s="4"/>
+      <x:c r="R62" s="4"/>
+      <x:c r="S62" s="4"/>
+      <x:c r="T62" s="4"/>
       <x:c r="U62" s="9"/>
       <x:c r="V62" s="9"/>
       <x:c r="W62" s="9"/>
@@ -3746,27 +3478,13 @@
       <x:c r="K63" s="4"/>
       <x:c r="L63" s="4"/>
       <x:c r="M63" s="4"/>
-      <x:c r="N63" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O63" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P63" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q63" s="4" t="str">
-        <x:v>-2,4</x:v>
-      </x:c>
-      <x:c r="R63" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S63" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T63" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N63" s="4"/>
+      <x:c r="O63" s="5"/>
+      <x:c r="P63" s="4"/>
+      <x:c r="Q63" s="4"/>
+      <x:c r="R63" s="4"/>
+      <x:c r="S63" s="4"/>
+      <x:c r="T63" s="4"/>
       <x:c r="U63" s="9"/>
       <x:c r="V63" s="9"/>
       <x:c r="W63" s="9"/>
@@ -3785,27 +3503,13 @@
       <x:c r="K64" s="4"/>
       <x:c r="L64" s="4"/>
       <x:c r="M64" s="4"/>
-      <x:c r="N64" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O64" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P64" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q64" s="4" t="str">
-        <x:v>-2,6</x:v>
-      </x:c>
-      <x:c r="R64" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S64" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T64" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N64" s="4"/>
+      <x:c r="O64" s="5"/>
+      <x:c r="P64" s="4"/>
+      <x:c r="Q64" s="4"/>
+      <x:c r="R64" s="4"/>
+      <x:c r="S64" s="4"/>
+      <x:c r="T64" s="4"/>
       <x:c r="U64" s="9"/>
       <x:c r="V64" s="9"/>
       <x:c r="W64" s="9"/>
@@ -3824,27 +3528,13 @@
       <x:c r="K65" s="4"/>
       <x:c r="L65" s="4"/>
       <x:c r="M65" s="4"/>
-      <x:c r="N65" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O65" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P65" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q65" s="4" t="str">
-        <x:v>-2,8</x:v>
-      </x:c>
-      <x:c r="R65" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S65" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T65" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N65" s="4"/>
+      <x:c r="O65" s="5"/>
+      <x:c r="P65" s="4"/>
+      <x:c r="Q65" s="4"/>
+      <x:c r="R65" s="4"/>
+      <x:c r="S65" s="4"/>
+      <x:c r="T65" s="4"/>
       <x:c r="U65" s="9"/>
       <x:c r="V65" s="9"/>
       <x:c r="W65" s="9"/>
@@ -3863,27 +3553,13 @@
       <x:c r="K66" s="4"/>
       <x:c r="L66" s="4"/>
       <x:c r="M66" s="4"/>
-      <x:c r="N66" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O66" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P66" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q66" s="4" t="str">
-        <x:v>-2,10</x:v>
-      </x:c>
-      <x:c r="R66" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S66" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T66" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N66" s="4"/>
+      <x:c r="O66" s="5"/>
+      <x:c r="P66" s="4"/>
+      <x:c r="Q66" s="4"/>
+      <x:c r="R66" s="4"/>
+      <x:c r="S66" s="4"/>
+      <x:c r="T66" s="4"/>
       <x:c r="U66" s="9"/>
       <x:c r="V66" s="9"/>
       <x:c r="W66" s="9"/>
@@ -3902,27 +3578,13 @@
       <x:c r="K67" s="4"/>
       <x:c r="L67" s="4"/>
       <x:c r="M67" s="4"/>
-      <x:c r="N67" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O67" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P67" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q67" s="4" t="str">
-        <x:v>-2,12</x:v>
-      </x:c>
-      <x:c r="R67" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S67" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T67" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N67" s="4"/>
+      <x:c r="O67" s="5"/>
+      <x:c r="P67" s="4"/>
+      <x:c r="Q67" s="4"/>
+      <x:c r="R67" s="4"/>
+      <x:c r="S67" s="4"/>
+      <x:c r="T67" s="4"/>
       <x:c r="U67" s="9"/>
       <x:c r="V67" s="9"/>
       <x:c r="W67" s="9"/>
@@ -3941,27 +3603,13 @@
       <x:c r="K68" s="4"/>
       <x:c r="L68" s="4"/>
       <x:c r="M68" s="4"/>
-      <x:c r="N68" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O68" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P68" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q68" s="4" t="str">
-        <x:v>-2,14</x:v>
-      </x:c>
-      <x:c r="R68" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S68" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T68" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N68" s="4"/>
+      <x:c r="O68" s="5"/>
+      <x:c r="P68" s="4"/>
+      <x:c r="Q68" s="4"/>
+      <x:c r="R68" s="4"/>
+      <x:c r="S68" s="4"/>
+      <x:c r="T68" s="4"/>
       <x:c r="U68" s="9"/>
       <x:c r="V68" s="9"/>
       <x:c r="W68" s="9"/>
@@ -3980,27 +3628,13 @@
       <x:c r="K69" s="4"/>
       <x:c r="L69" s="4"/>
       <x:c r="M69" s="4"/>
-      <x:c r="N69" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O69" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P69" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q69" s="4" t="str">
-        <x:v>-1,-15</x:v>
-      </x:c>
-      <x:c r="R69" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S69" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T69" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N69" s="4"/>
+      <x:c r="O69" s="5"/>
+      <x:c r="P69" s="4"/>
+      <x:c r="Q69" s="4"/>
+      <x:c r="R69" s="4"/>
+      <x:c r="S69" s="4"/>
+      <x:c r="T69" s="4"/>
       <x:c r="U69" s="9"/>
       <x:c r="V69" s="9"/>
       <x:c r="W69" s="9"/>
@@ -4019,27 +3653,13 @@
       <x:c r="K70" s="4"/>
       <x:c r="L70" s="4"/>
       <x:c r="M70" s="4"/>
-      <x:c r="N70" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O70" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P70" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q70" s="4" t="str">
-        <x:v>-1,-13</x:v>
-      </x:c>
-      <x:c r="R70" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S70" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T70" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N70" s="4"/>
+      <x:c r="O70" s="5"/>
+      <x:c r="P70" s="4"/>
+      <x:c r="Q70" s="4"/>
+      <x:c r="R70" s="4"/>
+      <x:c r="S70" s="4"/>
+      <x:c r="T70" s="4"/>
       <x:c r="U70" s="9"/>
       <x:c r="V70" s="9"/>
       <x:c r="W70" s="9"/>
@@ -4058,27 +3678,13 @@
       <x:c r="K71" s="4"/>
       <x:c r="L71" s="4"/>
       <x:c r="M71" s="4"/>
-      <x:c r="N71" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O71" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P71" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q71" s="4" t="str">
-        <x:v>-1,-11</x:v>
-      </x:c>
-      <x:c r="R71" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S71" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T71" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N71" s="4"/>
+      <x:c r="O71" s="5"/>
+      <x:c r="P71" s="4"/>
+      <x:c r="Q71" s="4"/>
+      <x:c r="R71" s="4"/>
+      <x:c r="S71" s="4"/>
+      <x:c r="T71" s="4"/>
       <x:c r="U71" s="9"/>
       <x:c r="V71" s="9"/>
       <x:c r="W71" s="9"/>
@@ -4097,27 +3703,13 @@
       <x:c r="K72" s="4"/>
       <x:c r="L72" s="4"/>
       <x:c r="M72" s="4"/>
-      <x:c r="N72" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O72" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P72" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q72" s="4" t="str">
-        <x:v>-1,-9</x:v>
-      </x:c>
-      <x:c r="R72" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S72" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T72" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N72" s="4"/>
+      <x:c r="O72" s="5"/>
+      <x:c r="P72" s="4"/>
+      <x:c r="Q72" s="4"/>
+      <x:c r="R72" s="4"/>
+      <x:c r="S72" s="4"/>
+      <x:c r="T72" s="4"/>
       <x:c r="U72" s="9"/>
       <x:c r="V72" s="9"/>
       <x:c r="W72" s="9"/>
@@ -4136,27 +3728,13 @@
       <x:c r="K73" s="4"/>
       <x:c r="L73" s="4"/>
       <x:c r="M73" s="4"/>
-      <x:c r="N73" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O73" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P73" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q73" s="4" t="str">
-        <x:v>-1,-7</x:v>
-      </x:c>
-      <x:c r="R73" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S73" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T73" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N73" s="4"/>
+      <x:c r="O73" s="5"/>
+      <x:c r="P73" s="4"/>
+      <x:c r="Q73" s="4"/>
+      <x:c r="R73" s="4"/>
+      <x:c r="S73" s="4"/>
+      <x:c r="T73" s="4"/>
       <x:c r="U73" s="9"/>
       <x:c r="V73" s="9"/>
       <x:c r="W73" s="9"/>
@@ -4175,27 +3753,13 @@
       <x:c r="K74" s="4"/>
       <x:c r="L74" s="4"/>
       <x:c r="M74" s="4"/>
-      <x:c r="N74" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O74" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P74" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q74" s="4" t="str">
-        <x:v>-1,-5</x:v>
-      </x:c>
-      <x:c r="R74" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S74" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T74" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N74" s="4"/>
+      <x:c r="O74" s="5"/>
+      <x:c r="P74" s="4"/>
+      <x:c r="Q74" s="4"/>
+      <x:c r="R74" s="4"/>
+      <x:c r="S74" s="4"/>
+      <x:c r="T74" s="4"/>
       <x:c r="U74" s="9"/>
       <x:c r="V74" s="9"/>
       <x:c r="W74" s="9"/>
@@ -4214,27 +3778,13 @@
       <x:c r="K75" s="4"/>
       <x:c r="L75" s="4"/>
       <x:c r="M75" s="4"/>
-      <x:c r="N75" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O75" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P75" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q75" s="4" t="str">
-        <x:v>-1,-3</x:v>
-      </x:c>
-      <x:c r="R75" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S75" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T75" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N75" s="4"/>
+      <x:c r="O75" s="5"/>
+      <x:c r="P75" s="4"/>
+      <x:c r="Q75" s="4"/>
+      <x:c r="R75" s="4"/>
+      <x:c r="S75" s="4"/>
+      <x:c r="T75" s="4"/>
       <x:c r="U75" s="9"/>
       <x:c r="V75" s="9"/>
       <x:c r="W75" s="9"/>
@@ -4253,27 +3803,13 @@
       <x:c r="K76" s="4"/>
       <x:c r="L76" s="4"/>
       <x:c r="M76" s="4"/>
-      <x:c r="N76" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O76" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P76" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q76" s="4" t="str">
-        <x:v>-1,-1</x:v>
-      </x:c>
-      <x:c r="R76" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S76" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T76" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N76" s="4"/>
+      <x:c r="O76" s="5"/>
+      <x:c r="P76" s="4"/>
+      <x:c r="Q76" s="4"/>
+      <x:c r="R76" s="4"/>
+      <x:c r="S76" s="4"/>
+      <x:c r="T76" s="4"/>
       <x:c r="U76" s="9"/>
       <x:c r="V76" s="9"/>
       <x:c r="W76" s="9"/>
@@ -4292,27 +3828,13 @@
       <x:c r="K77" s="4"/>
       <x:c r="L77" s="4"/>
       <x:c r="M77" s="4"/>
-      <x:c r="N77" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O77" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P77" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q77" s="4" t="str">
-        <x:v>-1,1</x:v>
-      </x:c>
-      <x:c r="R77" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S77" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T77" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N77" s="4"/>
+      <x:c r="O77" s="5"/>
+      <x:c r="P77" s="4"/>
+      <x:c r="Q77" s="4"/>
+      <x:c r="R77" s="4"/>
+      <x:c r="S77" s="4"/>
+      <x:c r="T77" s="4"/>
       <x:c r="U77" s="9"/>
       <x:c r="V77" s="9"/>
       <x:c r="W77" s="9"/>
@@ -4331,27 +3853,13 @@
       <x:c r="K78" s="4"/>
       <x:c r="L78" s="4"/>
       <x:c r="M78" s="4"/>
-      <x:c r="N78" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O78" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P78" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q78" s="4" t="str">
-        <x:v>-1,3</x:v>
-      </x:c>
-      <x:c r="R78" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S78" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T78" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N78" s="4"/>
+      <x:c r="O78" s="5"/>
+      <x:c r="P78" s="4"/>
+      <x:c r="Q78" s="4"/>
+      <x:c r="R78" s="4"/>
+      <x:c r="S78" s="4"/>
+      <x:c r="T78" s="4"/>
       <x:c r="U78" s="9"/>
       <x:c r="V78" s="9"/>
       <x:c r="W78" s="9"/>
@@ -4370,27 +3878,13 @@
       <x:c r="K79" s="4"/>
       <x:c r="L79" s="4"/>
       <x:c r="M79" s="4"/>
-      <x:c r="N79" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O79" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P79" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q79" s="4" t="str">
-        <x:v>-1,5</x:v>
-      </x:c>
-      <x:c r="R79" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S79" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T79" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N79" s="4"/>
+      <x:c r="O79" s="5"/>
+      <x:c r="P79" s="4"/>
+      <x:c r="Q79" s="4"/>
+      <x:c r="R79" s="4"/>
+      <x:c r="S79" s="4"/>
+      <x:c r="T79" s="4"/>
       <x:c r="U79" s="9"/>
       <x:c r="V79" s="9"/>
       <x:c r="W79" s="9"/>
@@ -4409,27 +3903,13 @@
       <x:c r="K80" s="4"/>
       <x:c r="L80" s="4"/>
       <x:c r="M80" s="4"/>
-      <x:c r="N80" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O80" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P80" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q80" s="4" t="str">
-        <x:v>-1,7</x:v>
-      </x:c>
-      <x:c r="R80" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S80" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T80" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N80" s="4"/>
+      <x:c r="O80" s="5"/>
+      <x:c r="P80" s="4"/>
+      <x:c r="Q80" s="4"/>
+      <x:c r="R80" s="4"/>
+      <x:c r="S80" s="4"/>
+      <x:c r="T80" s="4"/>
       <x:c r="U80" s="9"/>
       <x:c r="V80" s="9"/>
       <x:c r="W80" s="9"/>
@@ -4448,27 +3928,13 @@
       <x:c r="K81" s="4"/>
       <x:c r="L81" s="4"/>
       <x:c r="M81" s="4"/>
-      <x:c r="N81" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O81" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P81" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q81" s="4" t="str">
-        <x:v>-1,9</x:v>
-      </x:c>
-      <x:c r="R81" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S81" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T81" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N81" s="4"/>
+      <x:c r="O81" s="5"/>
+      <x:c r="P81" s="4"/>
+      <x:c r="Q81" s="4"/>
+      <x:c r="R81" s="4"/>
+      <x:c r="S81" s="4"/>
+      <x:c r="T81" s="4"/>
       <x:c r="U81" s="9"/>
       <x:c r="V81" s="9"/>
       <x:c r="W81" s="9"/>
@@ -4487,27 +3953,13 @@
       <x:c r="K82" s="4"/>
       <x:c r="L82" s="4"/>
       <x:c r="M82" s="4"/>
-      <x:c r="N82" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O82" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P82" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q82" s="4" t="str">
-        <x:v>-1,11</x:v>
-      </x:c>
-      <x:c r="R82" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S82" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T82" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N82" s="4"/>
+      <x:c r="O82" s="5"/>
+      <x:c r="P82" s="4"/>
+      <x:c r="Q82" s="4"/>
+      <x:c r="R82" s="4"/>
+      <x:c r="S82" s="4"/>
+      <x:c r="T82" s="4"/>
       <x:c r="U82" s="9"/>
       <x:c r="V82" s="9"/>
       <x:c r="W82" s="9"/>
@@ -4526,27 +3978,13 @@
       <x:c r="K83" s="4"/>
       <x:c r="L83" s="4"/>
       <x:c r="M83" s="4"/>
-      <x:c r="N83" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O83" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P83" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q83" s="4" t="str">
-        <x:v>-1,13</x:v>
-      </x:c>
-      <x:c r="R83" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S83" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T83" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N83" s="4"/>
+      <x:c r="O83" s="5"/>
+      <x:c r="P83" s="4"/>
+      <x:c r="Q83" s="4"/>
+      <x:c r="R83" s="4"/>
+      <x:c r="S83" s="4"/>
+      <x:c r="T83" s="4"/>
       <x:c r="U83" s="9"/>
       <x:c r="V83" s="9"/>
       <x:c r="W83" s="9"/>
@@ -4565,27 +4003,13 @@
       <x:c r="K84" s="4"/>
       <x:c r="L84" s="4"/>
       <x:c r="M84" s="4"/>
-      <x:c r="N84" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O84" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P84" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q84" s="4" t="str">
-        <x:v>-1,15</x:v>
-      </x:c>
-      <x:c r="R84" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S84" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T84" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N84" s="4"/>
+      <x:c r="O84" s="5"/>
+      <x:c r="P84" s="4"/>
+      <x:c r="Q84" s="4"/>
+      <x:c r="R84" s="4"/>
+      <x:c r="S84" s="4"/>
+      <x:c r="T84" s="4"/>
       <x:c r="U84" s="9"/>
       <x:c r="V84" s="9"/>
       <x:c r="W84" s="9"/>
@@ -4604,27 +4028,13 @@
       <x:c r="K85" s="4"/>
       <x:c r="L85" s="4"/>
       <x:c r="M85" s="4"/>
-      <x:c r="N85" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O85" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P85" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q85" s="4" t="str">
-        <x:v>0,-14</x:v>
-      </x:c>
-      <x:c r="R85" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S85" s="4" t="n">
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="T85" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N85" s="4"/>
+      <x:c r="O85" s="5"/>
+      <x:c r="P85" s="4"/>
+      <x:c r="Q85" s="4"/>
+      <x:c r="R85" s="4"/>
+      <x:c r="S85" s="4"/>
+      <x:c r="T85" s="4"/>
       <x:c r="U85" s="9"/>
       <x:c r="V85" s="9"/>
       <x:c r="W85" s="9"/>
@@ -4643,27 +4053,13 @@
       <x:c r="K86" s="4"/>
       <x:c r="L86" s="4"/>
       <x:c r="M86" s="4"/>
-      <x:c r="N86" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O86" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P86" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q86" s="4" t="str">
-        <x:v>0,-12</x:v>
-      </x:c>
-      <x:c r="R86" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S86" s="4" t="n">
-        <x:v>-12</x:v>
-      </x:c>
-      <x:c r="T86" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N86" s="4"/>
+      <x:c r="O86" s="5"/>
+      <x:c r="P86" s="4"/>
+      <x:c r="Q86" s="4"/>
+      <x:c r="R86" s="4"/>
+      <x:c r="S86" s="4"/>
+      <x:c r="T86" s="4"/>
       <x:c r="U86" s="9"/>
       <x:c r="V86" s="9"/>
       <x:c r="W86" s="9"/>
@@ -4682,27 +4078,13 @@
       <x:c r="K87" s="4"/>
       <x:c r="L87" s="4"/>
       <x:c r="M87" s="4"/>
-      <x:c r="N87" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O87" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P87" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q87" s="4" t="str">
-        <x:v>0,-10</x:v>
-      </x:c>
-      <x:c r="R87" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S87" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T87" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N87" s="4"/>
+      <x:c r="O87" s="5"/>
+      <x:c r="P87" s="4"/>
+      <x:c r="Q87" s="4"/>
+      <x:c r="R87" s="4"/>
+      <x:c r="S87" s="4"/>
+      <x:c r="T87" s="4"/>
       <x:c r="U87" s="9"/>
       <x:c r="V87" s="9"/>
       <x:c r="W87" s="9"/>
@@ -4721,27 +4103,13 @@
       <x:c r="K88" s="4"/>
       <x:c r="L88" s="4"/>
       <x:c r="M88" s="4"/>
-      <x:c r="N88" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O88" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P88" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q88" s="4" t="str">
-        <x:v>0,-8</x:v>
-      </x:c>
-      <x:c r="R88" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S88" s="4" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="T88" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N88" s="4"/>
+      <x:c r="O88" s="5"/>
+      <x:c r="P88" s="4"/>
+      <x:c r="Q88" s="4"/>
+      <x:c r="R88" s="4"/>
+      <x:c r="S88" s="4"/>
+      <x:c r="T88" s="4"/>
       <x:c r="U88" s="9"/>
       <x:c r="V88" s="9"/>
       <x:c r="W88" s="9"/>
@@ -4760,27 +4128,13 @@
       <x:c r="K89" s="4"/>
       <x:c r="L89" s="4"/>
       <x:c r="M89" s="4"/>
-      <x:c r="N89" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O89" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P89" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q89" s="4" t="str">
-        <x:v>0,-6</x:v>
-      </x:c>
-      <x:c r="R89" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S89" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T89" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N89" s="4"/>
+      <x:c r="O89" s="5"/>
+      <x:c r="P89" s="4"/>
+      <x:c r="Q89" s="4"/>
+      <x:c r="R89" s="4"/>
+      <x:c r="S89" s="4"/>
+      <x:c r="T89" s="4"/>
       <x:c r="U89" s="9"/>
       <x:c r="V89" s="9"/>
       <x:c r="W89" s="9"/>
@@ -4799,27 +4153,13 @@
       <x:c r="K90" s="4"/>
       <x:c r="L90" s="4"/>
       <x:c r="M90" s="4"/>
-      <x:c r="N90" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O90" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P90" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q90" s="4" t="str">
-        <x:v>0,-4</x:v>
-      </x:c>
-      <x:c r="R90" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S90" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T90" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N90" s="4"/>
+      <x:c r="O90" s="5"/>
+      <x:c r="P90" s="4"/>
+      <x:c r="Q90" s="4"/>
+      <x:c r="R90" s="4"/>
+      <x:c r="S90" s="4"/>
+      <x:c r="T90" s="4"/>
       <x:c r="U90" s="9"/>
       <x:c r="V90" s="9"/>
       <x:c r="W90" s="9"/>
@@ -4838,27 +4178,13 @@
       <x:c r="K91" s="4"/>
       <x:c r="L91" s="4"/>
       <x:c r="M91" s="4"/>
-      <x:c r="N91" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O91" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P91" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q91" s="4" t="str">
-        <x:v>0,-2</x:v>
-      </x:c>
-      <x:c r="R91" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S91" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="T91" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N91" s="4"/>
+      <x:c r="O91" s="5"/>
+      <x:c r="P91" s="4"/>
+      <x:c r="Q91" s="4"/>
+      <x:c r="R91" s="4"/>
+      <x:c r="S91" s="4"/>
+      <x:c r="T91" s="4"/>
       <x:c r="U91" s="9"/>
       <x:c r="V91" s="9"/>
       <x:c r="W91" s="9"/>
@@ -4877,27 +4203,13 @@
       <x:c r="K92" s="4"/>
       <x:c r="L92" s="4"/>
       <x:c r="M92" s="4"/>
-      <x:c r="N92" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O92" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P92" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q92" s="4" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="R92" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S92" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T92" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N92" s="4"/>
+      <x:c r="O92" s="5"/>
+      <x:c r="P92" s="4"/>
+      <x:c r="Q92" s="4"/>
+      <x:c r="R92" s="4"/>
+      <x:c r="S92" s="4"/>
+      <x:c r="T92" s="4"/>
       <x:c r="U92" s="9"/>
       <x:c r="V92" s="9"/>
       <x:c r="W92" s="9"/>
@@ -4916,27 +4228,13 @@
       <x:c r="K93" s="4"/>
       <x:c r="L93" s="4"/>
       <x:c r="M93" s="4"/>
-      <x:c r="N93" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O93" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P93" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q93" s="4" t="str">
-        <x:v>0,2</x:v>
-      </x:c>
-      <x:c r="R93" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S93" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T93" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N93" s="4"/>
+      <x:c r="O93" s="5"/>
+      <x:c r="P93" s="4"/>
+      <x:c r="Q93" s="4"/>
+      <x:c r="R93" s="4"/>
+      <x:c r="S93" s="4"/>
+      <x:c r="T93" s="4"/>
       <x:c r="U93" s="9"/>
       <x:c r="V93" s="9"/>
       <x:c r="W93" s="9"/>
@@ -4955,27 +4253,13 @@
       <x:c r="K94" s="4"/>
       <x:c r="L94" s="4"/>
       <x:c r="M94" s="4"/>
-      <x:c r="N94" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O94" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P94" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q94" s="4" t="str">
-        <x:v>0,4</x:v>
-      </x:c>
-      <x:c r="R94" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S94" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T94" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N94" s="4"/>
+      <x:c r="O94" s="5"/>
+      <x:c r="P94" s="4"/>
+      <x:c r="Q94" s="4"/>
+      <x:c r="R94" s="4"/>
+      <x:c r="S94" s="4"/>
+      <x:c r="T94" s="4"/>
       <x:c r="U94" s="9"/>
       <x:c r="V94" s="9"/>
       <x:c r="W94" s="9"/>
@@ -4994,27 +4278,13 @@
       <x:c r="K95" s="4"/>
       <x:c r="L95" s="4"/>
       <x:c r="M95" s="4"/>
-      <x:c r="N95" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O95" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P95" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q95" s="4" t="str">
-        <x:v>0,6</x:v>
-      </x:c>
-      <x:c r="R95" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S95" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T95" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N95" s="4"/>
+      <x:c r="O95" s="5"/>
+      <x:c r="P95" s="4"/>
+      <x:c r="Q95" s="4"/>
+      <x:c r="R95" s="4"/>
+      <x:c r="S95" s="4"/>
+      <x:c r="T95" s="4"/>
       <x:c r="U95" s="9"/>
       <x:c r="V95" s="9"/>
       <x:c r="W95" s="9"/>
@@ -5033,27 +4303,13 @@
       <x:c r="K96" s="4"/>
       <x:c r="L96" s="4"/>
       <x:c r="M96" s="4"/>
-      <x:c r="N96" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O96" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P96" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q96" s="4" t="str">
-        <x:v>0,8</x:v>
-      </x:c>
-      <x:c r="R96" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S96" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T96" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N96" s="4"/>
+      <x:c r="O96" s="5"/>
+      <x:c r="P96" s="4"/>
+      <x:c r="Q96" s="4"/>
+      <x:c r="R96" s="4"/>
+      <x:c r="S96" s="4"/>
+      <x:c r="T96" s="4"/>
       <x:c r="U96" s="9"/>
       <x:c r="V96" s="9"/>
       <x:c r="W96" s="9"/>
@@ -5072,27 +4328,13 @@
       <x:c r="K97" s="4"/>
       <x:c r="L97" s="4"/>
       <x:c r="M97" s="4"/>
-      <x:c r="N97" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O97" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P97" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q97" s="4" t="str">
-        <x:v>0,10</x:v>
-      </x:c>
-      <x:c r="R97" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S97" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T97" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N97" s="4"/>
+      <x:c r="O97" s="5"/>
+      <x:c r="P97" s="4"/>
+      <x:c r="Q97" s="4"/>
+      <x:c r="R97" s="4"/>
+      <x:c r="S97" s="4"/>
+      <x:c r="T97" s="4"/>
       <x:c r="U97" s="9"/>
       <x:c r="V97" s="9"/>
       <x:c r="W97" s="9"/>
@@ -5111,27 +4353,13 @@
       <x:c r="K98" s="4"/>
       <x:c r="L98" s="4"/>
       <x:c r="M98" s="4"/>
-      <x:c r="N98" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O98" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P98" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q98" s="4" t="str">
-        <x:v>0,12</x:v>
-      </x:c>
-      <x:c r="R98" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S98" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T98" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N98" s="4"/>
+      <x:c r="O98" s="5"/>
+      <x:c r="P98" s="4"/>
+      <x:c r="Q98" s="4"/>
+      <x:c r="R98" s="4"/>
+      <x:c r="S98" s="4"/>
+      <x:c r="T98" s="4"/>
       <x:c r="U98" s="9"/>
       <x:c r="V98" s="9"/>
       <x:c r="W98" s="9"/>
@@ -5150,27 +4378,13 @@
       <x:c r="K99" s="4"/>
       <x:c r="L99" s="4"/>
       <x:c r="M99" s="4"/>
-      <x:c r="N99" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O99" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P99" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q99" s="4" t="str">
-        <x:v>0,14</x:v>
-      </x:c>
-      <x:c r="R99" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S99" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T99" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N99" s="4"/>
+      <x:c r="O99" s="5"/>
+      <x:c r="P99" s="4"/>
+      <x:c r="Q99" s="4"/>
+      <x:c r="R99" s="4"/>
+      <x:c r="S99" s="4"/>
+      <x:c r="T99" s="4"/>
       <x:c r="U99" s="9"/>
       <x:c r="V99" s="9"/>
       <x:c r="W99" s="9"/>
@@ -5189,27 +4403,13 @@
       <x:c r="K100" s="4"/>
       <x:c r="L100" s="4"/>
       <x:c r="M100" s="4"/>
-      <x:c r="N100" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O100" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P100" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q100" s="4" t="str">
-        <x:v>1,-15</x:v>
-      </x:c>
-      <x:c r="R100" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S100" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T100" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N100" s="4"/>
+      <x:c r="O100" s="5"/>
+      <x:c r="P100" s="4"/>
+      <x:c r="Q100" s="4"/>
+      <x:c r="R100" s="4"/>
+      <x:c r="S100" s="4"/>
+      <x:c r="T100" s="4"/>
       <x:c r="U100" s="9"/>
       <x:c r="V100" s="9"/>
       <x:c r="W100" s="9"/>
@@ -5228,27 +4428,13 @@
       <x:c r="K101" s="4"/>
       <x:c r="L101" s="4"/>
       <x:c r="M101" s="4"/>
-      <x:c r="N101" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O101" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P101" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q101" s="4" t="str">
-        <x:v>1,-13</x:v>
-      </x:c>
-      <x:c r="R101" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S101" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T101" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N101" s="4"/>
+      <x:c r="O101" s="5"/>
+      <x:c r="P101" s="4"/>
+      <x:c r="Q101" s="4"/>
+      <x:c r="R101" s="4"/>
+      <x:c r="S101" s="4"/>
+      <x:c r="T101" s="4"/>
       <x:c r="U101" s="9"/>
       <x:c r="V101" s="9"/>
       <x:c r="W101" s="9"/>
@@ -5267,27 +4453,13 @@
       <x:c r="K102" s="4"/>
       <x:c r="L102" s="4"/>
       <x:c r="M102" s="4"/>
-      <x:c r="N102" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O102" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P102" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q102" s="4" t="str">
-        <x:v>1,-11</x:v>
-      </x:c>
-      <x:c r="R102" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S102" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T102" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N102" s="4"/>
+      <x:c r="O102" s="5"/>
+      <x:c r="P102" s="4"/>
+      <x:c r="Q102" s="4"/>
+      <x:c r="R102" s="4"/>
+      <x:c r="S102" s="4"/>
+      <x:c r="T102" s="4"/>
       <x:c r="U102" s="9"/>
       <x:c r="V102" s="9"/>
       <x:c r="W102" s="9"/>
@@ -5306,27 +4478,13 @@
       <x:c r="K103" s="4"/>
       <x:c r="L103" s="4"/>
       <x:c r="M103" s="4"/>
-      <x:c r="N103" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O103" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P103" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q103" s="4" t="str">
-        <x:v>1,-9</x:v>
-      </x:c>
-      <x:c r="R103" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S103" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T103" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N103" s="4"/>
+      <x:c r="O103" s="5"/>
+      <x:c r="P103" s="4"/>
+      <x:c r="Q103" s="4"/>
+      <x:c r="R103" s="4"/>
+      <x:c r="S103" s="4"/>
+      <x:c r="T103" s="4"/>
       <x:c r="U103" s="9"/>
       <x:c r="V103" s="9"/>
       <x:c r="W103" s="9"/>
@@ -5345,27 +4503,13 @@
       <x:c r="K104" s="4"/>
       <x:c r="L104" s="4"/>
       <x:c r="M104" s="4"/>
-      <x:c r="N104" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O104" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P104" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q104" s="4" t="str">
-        <x:v>1,-7</x:v>
-      </x:c>
-      <x:c r="R104" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S104" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T104" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N104" s="4"/>
+      <x:c r="O104" s="5"/>
+      <x:c r="P104" s="4"/>
+      <x:c r="Q104" s="4"/>
+      <x:c r="R104" s="4"/>
+      <x:c r="S104" s="4"/>
+      <x:c r="T104" s="4"/>
       <x:c r="U104" s="9"/>
       <x:c r="V104" s="9"/>
       <x:c r="W104" s="9"/>
@@ -5384,27 +4528,13 @@
       <x:c r="K105" s="4"/>
       <x:c r="L105" s="4"/>
       <x:c r="M105" s="4"/>
-      <x:c r="N105" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O105" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P105" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q105" s="4" t="str">
-        <x:v>1,-5</x:v>
-      </x:c>
-      <x:c r="R105" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S105" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T105" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N105" s="4"/>
+      <x:c r="O105" s="5"/>
+      <x:c r="P105" s="4"/>
+      <x:c r="Q105" s="4"/>
+      <x:c r="R105" s="4"/>
+      <x:c r="S105" s="4"/>
+      <x:c r="T105" s="4"/>
       <x:c r="U105" s="9"/>
       <x:c r="V105" s="9"/>
       <x:c r="W105" s="9"/>
@@ -5423,27 +4553,13 @@
       <x:c r="K106" s="4"/>
       <x:c r="L106" s="4"/>
       <x:c r="M106" s="4"/>
-      <x:c r="N106" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O106" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P106" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q106" s="4" t="str">
-        <x:v>1,-3</x:v>
-      </x:c>
-      <x:c r="R106" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S106" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T106" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N106" s="4"/>
+      <x:c r="O106" s="5"/>
+      <x:c r="P106" s="4"/>
+      <x:c r="Q106" s="4"/>
+      <x:c r="R106" s="4"/>
+      <x:c r="S106" s="4"/>
+      <x:c r="T106" s="4"/>
       <x:c r="U106" s="9"/>
       <x:c r="V106" s="9"/>
       <x:c r="W106" s="9"/>
@@ -5462,27 +4578,13 @@
       <x:c r="K107" s="4"/>
       <x:c r="L107" s="4"/>
       <x:c r="M107" s="4"/>
-      <x:c r="N107" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O107" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P107" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q107" s="4" t="str">
-        <x:v>1,-1</x:v>
-      </x:c>
-      <x:c r="R107" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S107" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T107" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N107" s="4"/>
+      <x:c r="O107" s="5"/>
+      <x:c r="P107" s="4"/>
+      <x:c r="Q107" s="4"/>
+      <x:c r="R107" s="4"/>
+      <x:c r="S107" s="4"/>
+      <x:c r="T107" s="4"/>
       <x:c r="U107" s="9"/>
       <x:c r="V107" s="9"/>
       <x:c r="W107" s="9"/>
@@ -5501,27 +4603,13 @@
       <x:c r="K108" s="4"/>
       <x:c r="L108" s="4"/>
       <x:c r="M108" s="4"/>
-      <x:c r="N108" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O108" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P108" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q108" s="4" t="str">
-        <x:v>1,1</x:v>
-      </x:c>
-      <x:c r="R108" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S108" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T108" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N108" s="4"/>
+      <x:c r="O108" s="5"/>
+      <x:c r="P108" s="4"/>
+      <x:c r="Q108" s="4"/>
+      <x:c r="R108" s="4"/>
+      <x:c r="S108" s="4"/>
+      <x:c r="T108" s="4"/>
       <x:c r="U108" s="9"/>
       <x:c r="V108" s="9"/>
       <x:c r="W108" s="9"/>
@@ -5540,27 +4628,13 @@
       <x:c r="K109" s="4"/>
       <x:c r="L109" s="4"/>
       <x:c r="M109" s="4"/>
-      <x:c r="N109" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O109" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P109" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q109" s="4" t="str">
-        <x:v>1,3</x:v>
-      </x:c>
-      <x:c r="R109" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S109" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T109" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N109" s="4"/>
+      <x:c r="O109" s="5"/>
+      <x:c r="P109" s="4"/>
+      <x:c r="Q109" s="4"/>
+      <x:c r="R109" s="4"/>
+      <x:c r="S109" s="4"/>
+      <x:c r="T109" s="4"/>
       <x:c r="U109" s="9"/>
       <x:c r="V109" s="9"/>
       <x:c r="W109" s="9"/>
@@ -5579,27 +4653,13 @@
       <x:c r="K110" s="4"/>
       <x:c r="L110" s="4"/>
       <x:c r="M110" s="4"/>
-      <x:c r="N110" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O110" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P110" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q110" s="4" t="str">
-        <x:v>1,5</x:v>
-      </x:c>
-      <x:c r="R110" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S110" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T110" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N110" s="4"/>
+      <x:c r="O110" s="5"/>
+      <x:c r="P110" s="4"/>
+      <x:c r="Q110" s="4"/>
+      <x:c r="R110" s="4"/>
+      <x:c r="S110" s="4"/>
+      <x:c r="T110" s="4"/>
       <x:c r="U110" s="9"/>
       <x:c r="V110" s="9"/>
       <x:c r="W110" s="9"/>
@@ -5618,27 +4678,13 @@
       <x:c r="K111" s="4"/>
       <x:c r="L111" s="4"/>
       <x:c r="M111" s="4"/>
-      <x:c r="N111" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O111" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P111" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q111" s="4" t="str">
-        <x:v>1,7</x:v>
-      </x:c>
-      <x:c r="R111" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S111" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T111" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N111" s="4"/>
+      <x:c r="O111" s="5"/>
+      <x:c r="P111" s="4"/>
+      <x:c r="Q111" s="4"/>
+      <x:c r="R111" s="4"/>
+      <x:c r="S111" s="4"/>
+      <x:c r="T111" s="4"/>
       <x:c r="U111" s="9"/>
       <x:c r="V111" s="9"/>
       <x:c r="W111" s="9"/>
@@ -5657,27 +4703,13 @@
       <x:c r="K112" s="4"/>
       <x:c r="L112" s="4"/>
       <x:c r="M112" s="4"/>
-      <x:c r="N112" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O112" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P112" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q112" s="4" t="str">
-        <x:v>1,9</x:v>
-      </x:c>
-      <x:c r="R112" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S112" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T112" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N112" s="4"/>
+      <x:c r="O112" s="5"/>
+      <x:c r="P112" s="4"/>
+      <x:c r="Q112" s="4"/>
+      <x:c r="R112" s="4"/>
+      <x:c r="S112" s="4"/>
+      <x:c r="T112" s="4"/>
       <x:c r="U112" s="9"/>
       <x:c r="V112" s="9"/>
       <x:c r="W112" s="9"/>
@@ -5696,27 +4728,13 @@
       <x:c r="K113" s="4"/>
       <x:c r="L113" s="4"/>
       <x:c r="M113" s="4"/>
-      <x:c r="N113" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O113" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P113" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q113" s="4" t="str">
-        <x:v>1,11</x:v>
-      </x:c>
-      <x:c r="R113" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S113" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T113" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N113" s="4"/>
+      <x:c r="O113" s="5"/>
+      <x:c r="P113" s="4"/>
+      <x:c r="Q113" s="4"/>
+      <x:c r="R113" s="4"/>
+      <x:c r="S113" s="4"/>
+      <x:c r="T113" s="4"/>
       <x:c r="U113" s="9"/>
       <x:c r="V113" s="9"/>
       <x:c r="W113" s="9"/>
@@ -5735,27 +4753,13 @@
       <x:c r="K114" s="4"/>
       <x:c r="L114" s="4"/>
       <x:c r="M114" s="4"/>
-      <x:c r="N114" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O114" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P114" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q114" s="4" t="str">
-        <x:v>1,13</x:v>
-      </x:c>
-      <x:c r="R114" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S114" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T114" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N114" s="4"/>
+      <x:c r="O114" s="5"/>
+      <x:c r="P114" s="4"/>
+      <x:c r="Q114" s="4"/>
+      <x:c r="R114" s="4"/>
+      <x:c r="S114" s="4"/>
+      <x:c r="T114" s="4"/>
       <x:c r="U114" s="9"/>
       <x:c r="V114" s="9"/>
       <x:c r="W114" s="9"/>
@@ -5774,27 +4778,13 @@
       <x:c r="K115" s="4"/>
       <x:c r="L115" s="4"/>
       <x:c r="M115" s="4"/>
-      <x:c r="N115" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O115" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P115" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q115" s="4" t="str">
-        <x:v>1,15</x:v>
-      </x:c>
-      <x:c r="R115" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S115" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T115" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N115" s="4"/>
+      <x:c r="O115" s="5"/>
+      <x:c r="P115" s="4"/>
+      <x:c r="Q115" s="4"/>
+      <x:c r="R115" s="4"/>
+      <x:c r="S115" s="4"/>
+      <x:c r="T115" s="4"/>
       <x:c r="U115" s="9"/>
       <x:c r="V115" s="9"/>
       <x:c r="W115" s="9"/>
@@ -5813,27 +4803,13 @@
       <x:c r="K116" s="4"/>
       <x:c r="L116" s="4"/>
       <x:c r="M116" s="4"/>
-      <x:c r="N116" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O116" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P116" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q116" s="4" t="str">
-        <x:v>2,-14</x:v>
-      </x:c>
-      <x:c r="R116" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S116" s="4" t="n">
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="T116" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N116" s="4"/>
+      <x:c r="O116" s="5"/>
+      <x:c r="P116" s="4"/>
+      <x:c r="Q116" s="4"/>
+      <x:c r="R116" s="4"/>
+      <x:c r="S116" s="4"/>
+      <x:c r="T116" s="4"/>
       <x:c r="U116" s="9"/>
       <x:c r="V116" s="9"/>
       <x:c r="W116" s="9"/>
@@ -5852,27 +4828,13 @@
       <x:c r="K117" s="4"/>
       <x:c r="L117" s="4"/>
       <x:c r="M117" s="4"/>
-      <x:c r="N117" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O117" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P117" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q117" s="4" t="str">
-        <x:v>2,-12</x:v>
-      </x:c>
-      <x:c r="R117" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S117" s="4" t="n">
-        <x:v>-12</x:v>
-      </x:c>
-      <x:c r="T117" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N117" s="4"/>
+      <x:c r="O117" s="5"/>
+      <x:c r="P117" s="4"/>
+      <x:c r="Q117" s="4"/>
+      <x:c r="R117" s="4"/>
+      <x:c r="S117" s="4"/>
+      <x:c r="T117" s="4"/>
       <x:c r="U117" s="9"/>
       <x:c r="V117" s="9"/>
       <x:c r="W117" s="9"/>
@@ -5891,27 +4853,13 @@
       <x:c r="K118" s="4"/>
       <x:c r="L118" s="4"/>
       <x:c r="M118" s="4"/>
-      <x:c r="N118" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O118" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P118" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q118" s="4" t="str">
-        <x:v>2,-10</x:v>
-      </x:c>
-      <x:c r="R118" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S118" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T118" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N118" s="4"/>
+      <x:c r="O118" s="5"/>
+      <x:c r="P118" s="4"/>
+      <x:c r="Q118" s="4"/>
+      <x:c r="R118" s="4"/>
+      <x:c r="S118" s="4"/>
+      <x:c r="T118" s="4"/>
       <x:c r="U118" s="9"/>
       <x:c r="V118" s="9"/>
       <x:c r="W118" s="9"/>
@@ -5930,27 +4878,13 @@
       <x:c r="K119" s="4"/>
       <x:c r="L119" s="4"/>
       <x:c r="M119" s="4"/>
-      <x:c r="N119" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O119" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P119" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q119" s="4" t="str">
-        <x:v>2,-8</x:v>
-      </x:c>
-      <x:c r="R119" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S119" s="4" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="T119" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N119" s="4"/>
+      <x:c r="O119" s="5"/>
+      <x:c r="P119" s="4"/>
+      <x:c r="Q119" s="4"/>
+      <x:c r="R119" s="4"/>
+      <x:c r="S119" s="4"/>
+      <x:c r="T119" s="4"/>
       <x:c r="U119" s="9"/>
       <x:c r="V119" s="9"/>
       <x:c r="W119" s="9"/>
@@ -5969,27 +4903,13 @@
       <x:c r="K120" s="4"/>
       <x:c r="L120" s="4"/>
       <x:c r="M120" s="4"/>
-      <x:c r="N120" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O120" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P120" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q120" s="4" t="str">
-        <x:v>2,-6</x:v>
-      </x:c>
-      <x:c r="R120" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S120" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T120" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N120" s="4"/>
+      <x:c r="O120" s="5"/>
+      <x:c r="P120" s="4"/>
+      <x:c r="Q120" s="4"/>
+      <x:c r="R120" s="4"/>
+      <x:c r="S120" s="4"/>
+      <x:c r="T120" s="4"/>
       <x:c r="U120" s="9"/>
       <x:c r="V120" s="9"/>
       <x:c r="W120" s="9"/>
@@ -6008,27 +4928,13 @@
       <x:c r="K121" s="4"/>
       <x:c r="L121" s="4"/>
       <x:c r="M121" s="4"/>
-      <x:c r="N121" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O121" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P121" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q121" s="4" t="str">
-        <x:v>2,-4</x:v>
-      </x:c>
-      <x:c r="R121" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S121" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T121" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N121" s="4"/>
+      <x:c r="O121" s="5"/>
+      <x:c r="P121" s="4"/>
+      <x:c r="Q121" s="4"/>
+      <x:c r="R121" s="4"/>
+      <x:c r="S121" s="4"/>
+      <x:c r="T121" s="4"/>
       <x:c r="U121" s="9"/>
       <x:c r="V121" s="9"/>
       <x:c r="W121" s="9"/>
@@ -6047,27 +4953,13 @@
       <x:c r="K122" s="4"/>
       <x:c r="L122" s="4"/>
       <x:c r="M122" s="4"/>
-      <x:c r="N122" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O122" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P122" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q122" s="4" t="str">
-        <x:v>2,-2</x:v>
-      </x:c>
-      <x:c r="R122" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S122" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="T122" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N122" s="4"/>
+      <x:c r="O122" s="5"/>
+      <x:c r="P122" s="4"/>
+      <x:c r="Q122" s="4"/>
+      <x:c r="R122" s="4"/>
+      <x:c r="S122" s="4"/>
+      <x:c r="T122" s="4"/>
       <x:c r="U122" s="9"/>
       <x:c r="V122" s="9"/>
       <x:c r="W122" s="9"/>
@@ -6086,27 +4978,13 @@
       <x:c r="K123" s="4"/>
       <x:c r="L123" s="4"/>
       <x:c r="M123" s="4"/>
-      <x:c r="N123" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O123" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P123" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q123" s="4" t="str">
-        <x:v>2,0</x:v>
-      </x:c>
-      <x:c r="R123" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S123" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T123" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N123" s="4"/>
+      <x:c r="O123" s="5"/>
+      <x:c r="P123" s="4"/>
+      <x:c r="Q123" s="4"/>
+      <x:c r="R123" s="4"/>
+      <x:c r="S123" s="4"/>
+      <x:c r="T123" s="4"/>
       <x:c r="U123" s="9"/>
       <x:c r="V123" s="9"/>
       <x:c r="W123" s="9"/>
@@ -6125,27 +5003,13 @@
       <x:c r="K124" s="4"/>
       <x:c r="L124" s="4"/>
       <x:c r="M124" s="4"/>
-      <x:c r="N124" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O124" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P124" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q124" s="4" t="str">
-        <x:v>2,2</x:v>
-      </x:c>
-      <x:c r="R124" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S124" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T124" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N124" s="4"/>
+      <x:c r="O124" s="5"/>
+      <x:c r="P124" s="4"/>
+      <x:c r="Q124" s="4"/>
+      <x:c r="R124" s="4"/>
+      <x:c r="S124" s="4"/>
+      <x:c r="T124" s="4"/>
       <x:c r="U124" s="9"/>
       <x:c r="V124" s="9"/>
       <x:c r="W124" s="9"/>
@@ -6164,27 +5028,13 @@
       <x:c r="K125" s="4"/>
       <x:c r="L125" s="4"/>
       <x:c r="M125" s="4"/>
-      <x:c r="N125" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O125" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P125" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q125" s="4" t="str">
-        <x:v>2,4</x:v>
-      </x:c>
-      <x:c r="R125" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S125" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T125" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N125" s="4"/>
+      <x:c r="O125" s="5"/>
+      <x:c r="P125" s="4"/>
+      <x:c r="Q125" s="4"/>
+      <x:c r="R125" s="4"/>
+      <x:c r="S125" s="4"/>
+      <x:c r="T125" s="4"/>
       <x:c r="U125" s="9"/>
       <x:c r="V125" s="9"/>
       <x:c r="W125" s="9"/>
@@ -6203,27 +5053,13 @@
       <x:c r="K126" s="4"/>
       <x:c r="L126" s="4"/>
       <x:c r="M126" s="4"/>
-      <x:c r="N126" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O126" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P126" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q126" s="4" t="str">
-        <x:v>2,6</x:v>
-      </x:c>
-      <x:c r="R126" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S126" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T126" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N126" s="4"/>
+      <x:c r="O126" s="5"/>
+      <x:c r="P126" s="4"/>
+      <x:c r="Q126" s="4"/>
+      <x:c r="R126" s="4"/>
+      <x:c r="S126" s="4"/>
+      <x:c r="T126" s="4"/>
       <x:c r="U126" s="9"/>
       <x:c r="V126" s="9"/>
       <x:c r="W126" s="9"/>
@@ -6242,27 +5078,13 @@
       <x:c r="K127" s="4"/>
       <x:c r="L127" s="4"/>
       <x:c r="M127" s="4"/>
-      <x:c r="N127" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O127" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P127" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q127" s="4" t="str">
-        <x:v>2,8</x:v>
-      </x:c>
-      <x:c r="R127" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S127" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T127" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N127" s="4"/>
+      <x:c r="O127" s="5"/>
+      <x:c r="P127" s="4"/>
+      <x:c r="Q127" s="4"/>
+      <x:c r="R127" s="4"/>
+      <x:c r="S127" s="4"/>
+      <x:c r="T127" s="4"/>
       <x:c r="U127" s="9"/>
       <x:c r="V127" s="9"/>
       <x:c r="W127" s="9"/>
@@ -6281,27 +5103,13 @@
       <x:c r="K128" s="4"/>
       <x:c r="L128" s="4"/>
       <x:c r="M128" s="4"/>
-      <x:c r="N128" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O128" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P128" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q128" s="4" t="str">
-        <x:v>2,10</x:v>
-      </x:c>
-      <x:c r="R128" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S128" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T128" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N128" s="4"/>
+      <x:c r="O128" s="5"/>
+      <x:c r="P128" s="4"/>
+      <x:c r="Q128" s="4"/>
+      <x:c r="R128" s="4"/>
+      <x:c r="S128" s="4"/>
+      <x:c r="T128" s="4"/>
       <x:c r="U128" s="9"/>
       <x:c r="V128" s="9"/>
       <x:c r="W128" s="9"/>
@@ -6320,27 +5128,13 @@
       <x:c r="K129" s="4"/>
       <x:c r="L129" s="4"/>
       <x:c r="M129" s="4"/>
-      <x:c r="N129" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O129" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P129" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q129" s="4" t="str">
-        <x:v>2,12</x:v>
-      </x:c>
-      <x:c r="R129" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S129" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T129" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N129" s="4"/>
+      <x:c r="O129" s="5"/>
+      <x:c r="P129" s="4"/>
+      <x:c r="Q129" s="4"/>
+      <x:c r="R129" s="4"/>
+      <x:c r="S129" s="4"/>
+      <x:c r="T129" s="4"/>
       <x:c r="U129" s="9"/>
       <x:c r="V129" s="9"/>
       <x:c r="W129" s="9"/>
@@ -6359,27 +5153,13 @@
       <x:c r="K130" s="4"/>
       <x:c r="L130" s="4"/>
       <x:c r="M130" s="4"/>
-      <x:c r="N130" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O130" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_048</x:v>
-      </x:c>
-      <x:c r="P130" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q130" s="4" t="str">
-        <x:v>2,14</x:v>
-      </x:c>
-      <x:c r="R130" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S130" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T130" s="4" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
+      <x:c r="N130" s="4"/>
+      <x:c r="O130" s="5"/>
+      <x:c r="P130" s="4"/>
+      <x:c r="Q130" s="4"/>
+      <x:c r="R130" s="4"/>
+      <x:c r="S130" s="4"/>
+      <x:c r="T130" s="4"/>
       <x:c r="U130" s="9"/>
       <x:c r="V130" s="9"/>
       <x:c r="W130" s="9"/>
@@ -6398,27 +5178,13 @@
       <x:c r="K131" s="4"/>
       <x:c r="L131" s="4"/>
       <x:c r="M131" s="4"/>
-      <x:c r="N131" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O131" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P131" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q131" s="4" t="str">
-        <x:v>3,-15</x:v>
-      </x:c>
-      <x:c r="R131" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S131" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T131" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N131" s="4"/>
+      <x:c r="O131" s="5"/>
+      <x:c r="P131" s="4"/>
+      <x:c r="Q131" s="4"/>
+      <x:c r="R131" s="4"/>
+      <x:c r="S131" s="4"/>
+      <x:c r="T131" s="4"/>
       <x:c r="U131" s="9"/>
       <x:c r="V131" s="9"/>
       <x:c r="W131" s="9"/>
@@ -6437,27 +5203,13 @@
       <x:c r="K132" s="4"/>
       <x:c r="L132" s="4"/>
       <x:c r="M132" s="4"/>
-      <x:c r="N132" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O132" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P132" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q132" s="4" t="str">
-        <x:v>3,-13</x:v>
-      </x:c>
-      <x:c r="R132" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S132" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T132" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N132" s="4"/>
+      <x:c r="O132" s="5"/>
+      <x:c r="P132" s="4"/>
+      <x:c r="Q132" s="4"/>
+      <x:c r="R132" s="4"/>
+      <x:c r="S132" s="4"/>
+      <x:c r="T132" s="4"/>
       <x:c r="U132" s="9"/>
       <x:c r="V132" s="9"/>
       <x:c r="W132" s="9"/>
@@ -6476,27 +5228,13 @@
       <x:c r="K133" s="4"/>
       <x:c r="L133" s="4"/>
       <x:c r="M133" s="4"/>
-      <x:c r="N133" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O133" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P133" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q133" s="4" t="str">
-        <x:v>3,-11</x:v>
-      </x:c>
-      <x:c r="R133" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S133" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T133" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N133" s="4"/>
+      <x:c r="O133" s="5"/>
+      <x:c r="P133" s="4"/>
+      <x:c r="Q133" s="4"/>
+      <x:c r="R133" s="4"/>
+      <x:c r="S133" s="4"/>
+      <x:c r="T133" s="4"/>
       <x:c r="U133" s="9"/>
       <x:c r="V133" s="9"/>
       <x:c r="W133" s="9"/>
@@ -6515,27 +5253,13 @@
       <x:c r="K134" s="4"/>
       <x:c r="L134" s="4"/>
       <x:c r="M134" s="4"/>
-      <x:c r="N134" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O134" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P134" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q134" s="4" t="str">
-        <x:v>3,-9</x:v>
-      </x:c>
-      <x:c r="R134" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S134" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T134" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N134" s="4"/>
+      <x:c r="O134" s="5"/>
+      <x:c r="P134" s="4"/>
+      <x:c r="Q134" s="4"/>
+      <x:c r="R134" s="4"/>
+      <x:c r="S134" s="4"/>
+      <x:c r="T134" s="4"/>
       <x:c r="U134" s="9"/>
       <x:c r="V134" s="9"/>
       <x:c r="W134" s="9"/>
@@ -6554,27 +5278,13 @@
       <x:c r="K135" s="4"/>
       <x:c r="L135" s="4"/>
       <x:c r="M135" s="4"/>
-      <x:c r="N135" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O135" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P135" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q135" s="4" t="str">
-        <x:v>3,-7</x:v>
-      </x:c>
-      <x:c r="R135" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S135" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T135" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N135" s="4"/>
+      <x:c r="O135" s="5"/>
+      <x:c r="P135" s="4"/>
+      <x:c r="Q135" s="4"/>
+      <x:c r="R135" s="4"/>
+      <x:c r="S135" s="4"/>
+      <x:c r="T135" s="4"/>
       <x:c r="U135" s="9"/>
       <x:c r="V135" s="9"/>
       <x:c r="W135" s="9"/>
@@ -6593,27 +5303,13 @@
       <x:c r="K136" s="4"/>
       <x:c r="L136" s="4"/>
       <x:c r="M136" s="4"/>
-      <x:c r="N136" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O136" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P136" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q136" s="4" t="str">
-        <x:v>3,-5</x:v>
-      </x:c>
-      <x:c r="R136" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S136" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T136" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N136" s="4"/>
+      <x:c r="O136" s="5"/>
+      <x:c r="P136" s="4"/>
+      <x:c r="Q136" s="4"/>
+      <x:c r="R136" s="4"/>
+      <x:c r="S136" s="4"/>
+      <x:c r="T136" s="4"/>
       <x:c r="U136" s="9"/>
       <x:c r="V136" s="9"/>
       <x:c r="W136" s="9"/>
@@ -6632,27 +5328,13 @@
       <x:c r="K137" s="4"/>
       <x:c r="L137" s="4"/>
       <x:c r="M137" s="4"/>
-      <x:c r="N137" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O137" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P137" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q137" s="4" t="str">
-        <x:v>3,-3</x:v>
-      </x:c>
-      <x:c r="R137" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S137" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T137" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N137" s="4"/>
+      <x:c r="O137" s="5"/>
+      <x:c r="P137" s="4"/>
+      <x:c r="Q137" s="4"/>
+      <x:c r="R137" s="4"/>
+      <x:c r="S137" s="4"/>
+      <x:c r="T137" s="4"/>
       <x:c r="U137" s="9"/>
       <x:c r="V137" s="9"/>
       <x:c r="W137" s="9"/>
@@ -6671,27 +5353,13 @@
       <x:c r="K138" s="4"/>
       <x:c r="L138" s="4"/>
       <x:c r="M138" s="4"/>
-      <x:c r="N138" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O138" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P138" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q138" s="4" t="str">
-        <x:v>3,-1</x:v>
-      </x:c>
-      <x:c r="R138" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S138" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T138" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N138" s="4"/>
+      <x:c r="O138" s="5"/>
+      <x:c r="P138" s="4"/>
+      <x:c r="Q138" s="4"/>
+      <x:c r="R138" s="4"/>
+      <x:c r="S138" s="4"/>
+      <x:c r="T138" s="4"/>
       <x:c r="U138" s="9"/>
       <x:c r="V138" s="9"/>
       <x:c r="W138" s="9"/>
@@ -6710,27 +5378,13 @@
       <x:c r="K139" s="4"/>
       <x:c r="L139" s="4"/>
       <x:c r="M139" s="4"/>
-      <x:c r="N139" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O139" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P139" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q139" s="4" t="str">
-        <x:v>3,1</x:v>
-      </x:c>
-      <x:c r="R139" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S139" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T139" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N139" s="4"/>
+      <x:c r="O139" s="5"/>
+      <x:c r="P139" s="4"/>
+      <x:c r="Q139" s="4"/>
+      <x:c r="R139" s="4"/>
+      <x:c r="S139" s="4"/>
+      <x:c r="T139" s="4"/>
       <x:c r="U139" s="9"/>
       <x:c r="V139" s="9"/>
       <x:c r="W139" s="9"/>
@@ -6749,27 +5403,13 @@
       <x:c r="K140" s="4"/>
       <x:c r="L140" s="4"/>
       <x:c r="M140" s="4"/>
-      <x:c r="N140" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O140" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P140" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q140" s="4" t="str">
-        <x:v>3,3</x:v>
-      </x:c>
-      <x:c r="R140" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S140" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T140" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N140" s="4"/>
+      <x:c r="O140" s="5"/>
+      <x:c r="P140" s="4"/>
+      <x:c r="Q140" s="4"/>
+      <x:c r="R140" s="4"/>
+      <x:c r="S140" s="4"/>
+      <x:c r="T140" s="4"/>
       <x:c r="U140" s="9"/>
       <x:c r="V140" s="9"/>
       <x:c r="W140" s="9"/>
@@ -6788,27 +5428,13 @@
       <x:c r="K141" s="4"/>
       <x:c r="L141" s="4"/>
       <x:c r="M141" s="4"/>
-      <x:c r="N141" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O141" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P141" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q141" s="4" t="str">
-        <x:v>3,5</x:v>
-      </x:c>
-      <x:c r="R141" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S141" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T141" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N141" s="4"/>
+      <x:c r="O141" s="5"/>
+      <x:c r="P141" s="4"/>
+      <x:c r="Q141" s="4"/>
+      <x:c r="R141" s="4"/>
+      <x:c r="S141" s="4"/>
+      <x:c r="T141" s="4"/>
       <x:c r="U141" s="9"/>
       <x:c r="V141" s="9"/>
       <x:c r="W141" s="9"/>
@@ -6827,27 +5453,13 @@
       <x:c r="K142" s="4"/>
       <x:c r="L142" s="4"/>
       <x:c r="M142" s="4"/>
-      <x:c r="N142" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O142" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P142" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q142" s="4" t="str">
-        <x:v>3,7</x:v>
-      </x:c>
-      <x:c r="R142" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S142" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T142" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N142" s="4"/>
+      <x:c r="O142" s="5"/>
+      <x:c r="P142" s="4"/>
+      <x:c r="Q142" s="4"/>
+      <x:c r="R142" s="4"/>
+      <x:c r="S142" s="4"/>
+      <x:c r="T142" s="4"/>
       <x:c r="U142" s="9"/>
       <x:c r="V142" s="9"/>
       <x:c r="W142" s="9"/>
@@ -6866,27 +5478,13 @@
       <x:c r="K143" s="4"/>
       <x:c r="L143" s="4"/>
       <x:c r="M143" s="4"/>
-      <x:c r="N143" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O143" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P143" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q143" s="4" t="str">
-        <x:v>3,9</x:v>
-      </x:c>
-      <x:c r="R143" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S143" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T143" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N143" s="4"/>
+      <x:c r="O143" s="5"/>
+      <x:c r="P143" s="4"/>
+      <x:c r="Q143" s="4"/>
+      <x:c r="R143" s="4"/>
+      <x:c r="S143" s="4"/>
+      <x:c r="T143" s="4"/>
       <x:c r="U143" s="9"/>
       <x:c r="V143" s="9"/>
       <x:c r="W143" s="9"/>
@@ -6905,27 +5503,13 @@
       <x:c r="K144" s="4"/>
       <x:c r="L144" s="4"/>
       <x:c r="M144" s="4"/>
-      <x:c r="N144" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O144" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P144" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q144" s="4" t="str">
-        <x:v>3,11</x:v>
-      </x:c>
-      <x:c r="R144" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S144" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T144" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N144" s="4"/>
+      <x:c r="O144" s="5"/>
+      <x:c r="P144" s="4"/>
+      <x:c r="Q144" s="4"/>
+      <x:c r="R144" s="4"/>
+      <x:c r="S144" s="4"/>
+      <x:c r="T144" s="4"/>
       <x:c r="U144" s="9"/>
       <x:c r="V144" s="9"/>
       <x:c r="W144" s="9"/>
@@ -6944,27 +5528,13 @@
       <x:c r="K145" s="4"/>
       <x:c r="L145" s="4"/>
       <x:c r="M145" s="4"/>
-      <x:c r="N145" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O145" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P145" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q145" s="4" t="str">
-        <x:v>3,13</x:v>
-      </x:c>
-      <x:c r="R145" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S145" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T145" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N145" s="4"/>
+      <x:c r="O145" s="5"/>
+      <x:c r="P145" s="4"/>
+      <x:c r="Q145" s="4"/>
+      <x:c r="R145" s="4"/>
+      <x:c r="S145" s="4"/>
+      <x:c r="T145" s="4"/>
       <x:c r="U145" s="9"/>
       <x:c r="V145" s="9"/>
       <x:c r="W145" s="9"/>
@@ -6983,27 +5553,13 @@
       <x:c r="K146" s="4"/>
       <x:c r="L146" s="4"/>
       <x:c r="M146" s="4"/>
-      <x:c r="N146" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O146" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_001</x:v>
-      </x:c>
-      <x:c r="P146" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q146" s="4" t="str">
-        <x:v>3,15</x:v>
-      </x:c>
-      <x:c r="R146" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S146" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T146" s="4" t="str">
-        <x:v>0.25,0</x:v>
-      </x:c>
+      <x:c r="N146" s="4"/>
+      <x:c r="O146" s="5"/>
+      <x:c r="P146" s="4"/>
+      <x:c r="Q146" s="4"/>
+      <x:c r="R146" s="4"/>
+      <x:c r="S146" s="4"/>
+      <x:c r="T146" s="4"/>
       <x:c r="U146" s="9"/>
       <x:c r="V146" s="9"/>
       <x:c r="W146" s="9"/>
@@ -7022,27 +5578,13 @@
       <x:c r="K147" s="4"/>
       <x:c r="L147" s="4"/>
       <x:c r="M147" s="4"/>
-      <x:c r="N147" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O147" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P147" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q147" s="4" t="str">
-        <x:v>4,-14</x:v>
-      </x:c>
-      <x:c r="R147" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S147" s="4" t="n">
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="T147" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N147" s="4"/>
+      <x:c r="O147" s="5"/>
+      <x:c r="P147" s="4"/>
+      <x:c r="Q147" s="4"/>
+      <x:c r="R147" s="4"/>
+      <x:c r="S147" s="4"/>
+      <x:c r="T147" s="4"/>
       <x:c r="U147" s="9"/>
       <x:c r="V147" s="9"/>
       <x:c r="W147" s="9"/>
@@ -7061,27 +5603,13 @@
       <x:c r="K148" s="4"/>
       <x:c r="L148" s="4"/>
       <x:c r="M148" s="4"/>
-      <x:c r="N148" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O148" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P148" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q148" s="4" t="str">
-        <x:v>4,-12</x:v>
-      </x:c>
-      <x:c r="R148" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S148" s="4" t="n">
-        <x:v>-12</x:v>
-      </x:c>
-      <x:c r="T148" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N148" s="4"/>
+      <x:c r="O148" s="5"/>
+      <x:c r="P148" s="4"/>
+      <x:c r="Q148" s="4"/>
+      <x:c r="R148" s="4"/>
+      <x:c r="S148" s="4"/>
+      <x:c r="T148" s="4"/>
       <x:c r="U148" s="9"/>
       <x:c r="V148" s="9"/>
       <x:c r="W148" s="9"/>
@@ -7100,27 +5628,13 @@
       <x:c r="K149" s="4"/>
       <x:c r="L149" s="4"/>
       <x:c r="M149" s="4"/>
-      <x:c r="N149" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O149" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P149" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q149" s="4" t="str">
-        <x:v>4,-10</x:v>
-      </x:c>
-      <x:c r="R149" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S149" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T149" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N149" s="4"/>
+      <x:c r="O149" s="5"/>
+      <x:c r="P149" s="4"/>
+      <x:c r="Q149" s="4"/>
+      <x:c r="R149" s="4"/>
+      <x:c r="S149" s="4"/>
+      <x:c r="T149" s="4"/>
       <x:c r="U149" s="9"/>
       <x:c r="V149" s="9"/>
       <x:c r="W149" s="9"/>
@@ -7139,27 +5653,13 @@
       <x:c r="K150" s="4"/>
       <x:c r="L150" s="4"/>
       <x:c r="M150" s="4"/>
-      <x:c r="N150" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O150" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P150" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q150" s="4" t="str">
-        <x:v>4,-8</x:v>
-      </x:c>
-      <x:c r="R150" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S150" s="4" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="T150" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N150" s="4"/>
+      <x:c r="O150" s="5"/>
+      <x:c r="P150" s="4"/>
+      <x:c r="Q150" s="4"/>
+      <x:c r="R150" s="4"/>
+      <x:c r="S150" s="4"/>
+      <x:c r="T150" s="4"/>
       <x:c r="U150" s="9"/>
       <x:c r="V150" s="9"/>
       <x:c r="W150" s="9"/>
@@ -7178,27 +5678,13 @@
       <x:c r="K151" s="4"/>
       <x:c r="L151" s="4"/>
       <x:c r="M151" s="4"/>
-      <x:c r="N151" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O151" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P151" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q151" s="4" t="str">
-        <x:v>4,-6</x:v>
-      </x:c>
-      <x:c r="R151" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S151" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T151" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N151" s="4"/>
+      <x:c r="O151" s="5"/>
+      <x:c r="P151" s="4"/>
+      <x:c r="Q151" s="4"/>
+      <x:c r="R151" s="4"/>
+      <x:c r="S151" s="4"/>
+      <x:c r="T151" s="4"/>
       <x:c r="U151" s="9"/>
       <x:c r="V151" s="9"/>
       <x:c r="W151" s="9"/>
@@ -7217,27 +5703,13 @@
       <x:c r="K152" s="4"/>
       <x:c r="L152" s="4"/>
       <x:c r="M152" s="4"/>
-      <x:c r="N152" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O152" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P152" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q152" s="4" t="str">
-        <x:v>4,-4</x:v>
-      </x:c>
-      <x:c r="R152" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S152" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T152" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N152" s="4"/>
+      <x:c r="O152" s="5"/>
+      <x:c r="P152" s="4"/>
+      <x:c r="Q152" s="4"/>
+      <x:c r="R152" s="4"/>
+      <x:c r="S152" s="4"/>
+      <x:c r="T152" s="4"/>
       <x:c r="U152" s="9"/>
       <x:c r="V152" s="9"/>
       <x:c r="W152" s="9"/>
@@ -7256,27 +5728,13 @@
       <x:c r="K153" s="4"/>
       <x:c r="L153" s="4"/>
       <x:c r="M153" s="4"/>
-      <x:c r="N153" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O153" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P153" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q153" s="4" t="str">
-        <x:v>4,-2</x:v>
-      </x:c>
-      <x:c r="R153" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S153" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="T153" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N153" s="4"/>
+      <x:c r="O153" s="5"/>
+      <x:c r="P153" s="4"/>
+      <x:c r="Q153" s="4"/>
+      <x:c r="R153" s="4"/>
+      <x:c r="S153" s="4"/>
+      <x:c r="T153" s="4"/>
       <x:c r="U153" s="9"/>
       <x:c r="V153" s="9"/>
       <x:c r="W153" s="9"/>
@@ -7295,27 +5753,13 @@
       <x:c r="K154" s="4"/>
       <x:c r="L154" s="4"/>
       <x:c r="M154" s="4"/>
-      <x:c r="N154" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O154" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P154" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q154" s="4" t="str">
-        <x:v>4,0</x:v>
-      </x:c>
-      <x:c r="R154" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S154" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T154" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N154" s="4"/>
+      <x:c r="O154" s="5"/>
+      <x:c r="P154" s="4"/>
+      <x:c r="Q154" s="4"/>
+      <x:c r="R154" s="4"/>
+      <x:c r="S154" s="4"/>
+      <x:c r="T154" s="4"/>
       <x:c r="U154" s="9"/>
       <x:c r="V154" s="9"/>
       <x:c r="W154" s="9"/>
@@ -7334,27 +5778,13 @@
       <x:c r="K155" s="4"/>
       <x:c r="L155" s="4"/>
       <x:c r="M155" s="4"/>
-      <x:c r="N155" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O155" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P155" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q155" s="4" t="str">
-        <x:v>4,2</x:v>
-      </x:c>
-      <x:c r="R155" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S155" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T155" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N155" s="4"/>
+      <x:c r="O155" s="5"/>
+      <x:c r="P155" s="4"/>
+      <x:c r="Q155" s="4"/>
+      <x:c r="R155" s="4"/>
+      <x:c r="S155" s="4"/>
+      <x:c r="T155" s="4"/>
       <x:c r="U155" s="9"/>
       <x:c r="V155" s="9"/>
       <x:c r="W155" s="9"/>
@@ -7373,27 +5803,13 @@
       <x:c r="K156" s="4"/>
       <x:c r="L156" s="4"/>
       <x:c r="M156" s="4"/>
-      <x:c r="N156" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O156" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P156" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q156" s="4" t="str">
-        <x:v>4,4</x:v>
-      </x:c>
-      <x:c r="R156" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S156" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T156" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N156" s="4"/>
+      <x:c r="O156" s="5"/>
+      <x:c r="P156" s="4"/>
+      <x:c r="Q156" s="4"/>
+      <x:c r="R156" s="4"/>
+      <x:c r="S156" s="4"/>
+      <x:c r="T156" s="4"/>
       <x:c r="U156" s="9"/>
       <x:c r="V156" s="9"/>
       <x:c r="W156" s="9"/>
@@ -7412,27 +5828,13 @@
       <x:c r="K157" s="4"/>
       <x:c r="L157" s="4"/>
       <x:c r="M157" s="4"/>
-      <x:c r="N157" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O157" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P157" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q157" s="4" t="str">
-        <x:v>4,6</x:v>
-      </x:c>
-      <x:c r="R157" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S157" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T157" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N157" s="4"/>
+      <x:c r="O157" s="5"/>
+      <x:c r="P157" s="4"/>
+      <x:c r="Q157" s="4"/>
+      <x:c r="R157" s="4"/>
+      <x:c r="S157" s="4"/>
+      <x:c r="T157" s="4"/>
       <x:c r="U157" s="9"/>
       <x:c r="V157" s="9"/>
       <x:c r="W157" s="9"/>
@@ -7451,27 +5853,13 @@
       <x:c r="K158" s="4"/>
       <x:c r="L158" s="4"/>
       <x:c r="M158" s="4"/>
-      <x:c r="N158" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O158" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P158" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q158" s="4" t="str">
-        <x:v>4,8</x:v>
-      </x:c>
-      <x:c r="R158" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S158" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T158" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N158" s="4"/>
+      <x:c r="O158" s="5"/>
+      <x:c r="P158" s="4"/>
+      <x:c r="Q158" s="4"/>
+      <x:c r="R158" s="4"/>
+      <x:c r="S158" s="4"/>
+      <x:c r="T158" s="4"/>
       <x:c r="U158" s="9"/>
       <x:c r="V158" s="9"/>
       <x:c r="W158" s="9"/>
@@ -7490,27 +5878,13 @@
       <x:c r="K159" s="4"/>
       <x:c r="L159" s="4"/>
       <x:c r="M159" s="4"/>
-      <x:c r="N159" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O159" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P159" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q159" s="4" t="str">
-        <x:v>4,10</x:v>
-      </x:c>
-      <x:c r="R159" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S159" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T159" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N159" s="4"/>
+      <x:c r="O159" s="5"/>
+      <x:c r="P159" s="4"/>
+      <x:c r="Q159" s="4"/>
+      <x:c r="R159" s="4"/>
+      <x:c r="S159" s="4"/>
+      <x:c r="T159" s="4"/>
       <x:c r="U159" s="9"/>
       <x:c r="V159" s="9"/>
       <x:c r="W159" s="9"/>
@@ -7529,27 +5903,13 @@
       <x:c r="K160" s="4"/>
       <x:c r="L160" s="4"/>
       <x:c r="M160" s="4"/>
-      <x:c r="N160" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O160" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P160" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q160" s="4" t="str">
-        <x:v>4,12</x:v>
-      </x:c>
-      <x:c r="R160" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S160" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T160" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N160" s="4"/>
+      <x:c r="O160" s="5"/>
+      <x:c r="P160" s="4"/>
+      <x:c r="Q160" s="4"/>
+      <x:c r="R160" s="4"/>
+      <x:c r="S160" s="4"/>
+      <x:c r="T160" s="4"/>
       <x:c r="U160" s="9"/>
       <x:c r="V160" s="9"/>
       <x:c r="W160" s="9"/>
@@ -7568,27 +5928,13 @@
       <x:c r="K161" s="4"/>
       <x:c r="L161" s="4"/>
       <x:c r="M161" s="4"/>
-      <x:c r="N161" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O161" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_017</x:v>
-      </x:c>
-      <x:c r="P161" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q161" s="4" t="str">
-        <x:v>4,14</x:v>
-      </x:c>
-      <x:c r="R161" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S161" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T161" s="4" t="str">
-        <x:v>0,0.5</x:v>
-      </x:c>
+      <x:c r="N161" s="4"/>
+      <x:c r="O161" s="5"/>
+      <x:c r="P161" s="4"/>
+      <x:c r="Q161" s="4"/>
+      <x:c r="R161" s="4"/>
+      <x:c r="S161" s="4"/>
+      <x:c r="T161" s="4"/>
       <x:c r="U161" s="9"/>
       <x:c r="V161" s="9"/>
       <x:c r="W161" s="9"/>
@@ -7607,27 +5953,13 @@
       <x:c r="K162" s="4"/>
       <x:c r="L162" s="4"/>
       <x:c r="M162" s="4"/>
-      <x:c r="N162" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O162" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P162" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q162" s="4" t="str">
-        <x:v>5,-15</x:v>
-      </x:c>
-      <x:c r="R162" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S162" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T162" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N162" s="4"/>
+      <x:c r="O162" s="5"/>
+      <x:c r="P162" s="4"/>
+      <x:c r="Q162" s="4"/>
+      <x:c r="R162" s="4"/>
+      <x:c r="S162" s="4"/>
+      <x:c r="T162" s="4"/>
       <x:c r="U162" s="9"/>
       <x:c r="V162" s="9"/>
       <x:c r="W162" s="9"/>
@@ -7646,27 +5978,13 @@
       <x:c r="K163" s="4"/>
       <x:c r="L163" s="4"/>
       <x:c r="M163" s="4"/>
-      <x:c r="N163" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O163" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P163" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q163" s="4" t="str">
-        <x:v>5,-13</x:v>
-      </x:c>
-      <x:c r="R163" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S163" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T163" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N163" s="4"/>
+      <x:c r="O163" s="5"/>
+      <x:c r="P163" s="4"/>
+      <x:c r="Q163" s="4"/>
+      <x:c r="R163" s="4"/>
+      <x:c r="S163" s="4"/>
+      <x:c r="T163" s="4"/>
       <x:c r="U163" s="9"/>
       <x:c r="V163" s="9"/>
       <x:c r="W163" s="9"/>
@@ -7685,27 +6003,13 @@
       <x:c r="K164" s="4"/>
       <x:c r="L164" s="4"/>
       <x:c r="M164" s="4"/>
-      <x:c r="N164" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O164" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P164" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q164" s="4" t="str">
-        <x:v>5,-11</x:v>
-      </x:c>
-      <x:c r="R164" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S164" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T164" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N164" s="4"/>
+      <x:c r="O164" s="5"/>
+      <x:c r="P164" s="4"/>
+      <x:c r="Q164" s="4"/>
+      <x:c r="R164" s="4"/>
+      <x:c r="S164" s="4"/>
+      <x:c r="T164" s="4"/>
       <x:c r="U164" s="9"/>
       <x:c r="V164" s="9"/>
       <x:c r="W164" s="9"/>
@@ -7724,27 +6028,13 @@
       <x:c r="K165" s="4"/>
       <x:c r="L165" s="4"/>
       <x:c r="M165" s="4"/>
-      <x:c r="N165" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O165" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P165" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q165" s="4" t="str">
-        <x:v>5,-9</x:v>
-      </x:c>
-      <x:c r="R165" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S165" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T165" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N165" s="4"/>
+      <x:c r="O165" s="5"/>
+      <x:c r="P165" s="4"/>
+      <x:c r="Q165" s="4"/>
+      <x:c r="R165" s="4"/>
+      <x:c r="S165" s="4"/>
+      <x:c r="T165" s="4"/>
       <x:c r="U165" s="9"/>
       <x:c r="V165" s="9"/>
       <x:c r="W165" s="9"/>
@@ -7763,27 +6053,13 @@
       <x:c r="K166" s="4"/>
       <x:c r="L166" s="4"/>
       <x:c r="M166" s="4"/>
-      <x:c r="N166" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O166" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P166" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q166" s="4" t="str">
-        <x:v>5,-7</x:v>
-      </x:c>
-      <x:c r="R166" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S166" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T166" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N166" s="4"/>
+      <x:c r="O166" s="5"/>
+      <x:c r="P166" s="4"/>
+      <x:c r="Q166" s="4"/>
+      <x:c r="R166" s="4"/>
+      <x:c r="S166" s="4"/>
+      <x:c r="T166" s="4"/>
       <x:c r="U166" s="9"/>
       <x:c r="V166" s="9"/>
       <x:c r="W166" s="9"/>
@@ -7802,27 +6078,13 @@
       <x:c r="K167" s="4"/>
       <x:c r="L167" s="4"/>
       <x:c r="M167" s="4"/>
-      <x:c r="N167" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O167" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P167" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q167" s="4" t="str">
-        <x:v>5,-5</x:v>
-      </x:c>
-      <x:c r="R167" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S167" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T167" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N167" s="4"/>
+      <x:c r="O167" s="5"/>
+      <x:c r="P167" s="4"/>
+      <x:c r="Q167" s="4"/>
+      <x:c r="R167" s="4"/>
+      <x:c r="S167" s="4"/>
+      <x:c r="T167" s="4"/>
       <x:c r="U167" s="9"/>
       <x:c r="V167" s="9"/>
       <x:c r="W167" s="9"/>
@@ -7841,27 +6103,13 @@
       <x:c r="K168" s="4"/>
       <x:c r="L168" s="4"/>
       <x:c r="M168" s="4"/>
-      <x:c r="N168" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O168" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P168" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q168" s="4" t="str">
-        <x:v>5,-3</x:v>
-      </x:c>
-      <x:c r="R168" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S168" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T168" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N168" s="4"/>
+      <x:c r="O168" s="5"/>
+      <x:c r="P168" s="4"/>
+      <x:c r="Q168" s="4"/>
+      <x:c r="R168" s="4"/>
+      <x:c r="S168" s="4"/>
+      <x:c r="T168" s="4"/>
       <x:c r="U168" s="9"/>
       <x:c r="V168" s="9"/>
       <x:c r="W168" s="9"/>
@@ -7880,27 +6128,13 @@
       <x:c r="K169" s="4"/>
       <x:c r="L169" s="4"/>
       <x:c r="M169" s="4"/>
-      <x:c r="N169" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O169" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P169" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q169" s="4" t="str">
-        <x:v>5,-1</x:v>
-      </x:c>
-      <x:c r="R169" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S169" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T169" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N169" s="4"/>
+      <x:c r="O169" s="5"/>
+      <x:c r="P169" s="4"/>
+      <x:c r="Q169" s="4"/>
+      <x:c r="R169" s="4"/>
+      <x:c r="S169" s="4"/>
+      <x:c r="T169" s="4"/>
       <x:c r="U169" s="9"/>
       <x:c r="V169" s="9"/>
       <x:c r="W169" s="9"/>
@@ -7919,27 +6153,13 @@
       <x:c r="K170" s="4"/>
       <x:c r="L170" s="4"/>
       <x:c r="M170" s="4"/>
-      <x:c r="N170" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O170" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P170" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q170" s="4" t="str">
-        <x:v>5,1</x:v>
-      </x:c>
-      <x:c r="R170" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S170" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T170" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N170" s="4"/>
+      <x:c r="O170" s="5"/>
+      <x:c r="P170" s="4"/>
+      <x:c r="Q170" s="4"/>
+      <x:c r="R170" s="4"/>
+      <x:c r="S170" s="4"/>
+      <x:c r="T170" s="4"/>
       <x:c r="U170" s="9"/>
       <x:c r="V170" s="9"/>
       <x:c r="W170" s="9"/>
@@ -7958,27 +6178,13 @@
       <x:c r="K171" s="4"/>
       <x:c r="L171" s="4"/>
       <x:c r="M171" s="4"/>
-      <x:c r="N171" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O171" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P171" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q171" s="4" t="str">
-        <x:v>5,3</x:v>
-      </x:c>
-      <x:c r="R171" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S171" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T171" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N171" s="4"/>
+      <x:c r="O171" s="5"/>
+      <x:c r="P171" s="4"/>
+      <x:c r="Q171" s="4"/>
+      <x:c r="R171" s="4"/>
+      <x:c r="S171" s="4"/>
+      <x:c r="T171" s="4"/>
       <x:c r="U171" s="9"/>
       <x:c r="V171" s="9"/>
       <x:c r="W171" s="9"/>
@@ -7997,27 +6203,13 @@
       <x:c r="K172" s="4"/>
       <x:c r="L172" s="4"/>
       <x:c r="M172" s="4"/>
-      <x:c r="N172" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O172" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P172" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q172" s="4" t="str">
-        <x:v>5,5</x:v>
-      </x:c>
-      <x:c r="R172" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S172" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T172" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N172" s="4"/>
+      <x:c r="O172" s="5"/>
+      <x:c r="P172" s="4"/>
+      <x:c r="Q172" s="4"/>
+      <x:c r="R172" s="4"/>
+      <x:c r="S172" s="4"/>
+      <x:c r="T172" s="4"/>
       <x:c r="U172" s="9"/>
       <x:c r="V172" s="9"/>
       <x:c r="W172" s="9"/>
@@ -8036,27 +6228,13 @@
       <x:c r="K173" s="4"/>
       <x:c r="L173" s="4"/>
       <x:c r="M173" s="4"/>
-      <x:c r="N173" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O173" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P173" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q173" s="4" t="str">
-        <x:v>5,7</x:v>
-      </x:c>
-      <x:c r="R173" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S173" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T173" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N173" s="4"/>
+      <x:c r="O173" s="5"/>
+      <x:c r="P173" s="4"/>
+      <x:c r="Q173" s="4"/>
+      <x:c r="R173" s="4"/>
+      <x:c r="S173" s="4"/>
+      <x:c r="T173" s="4"/>
       <x:c r="U173" s="9"/>
       <x:c r="V173" s="9"/>
       <x:c r="W173" s="9"/>
@@ -8075,27 +6253,13 @@
       <x:c r="K174" s="4"/>
       <x:c r="L174" s="4"/>
       <x:c r="M174" s="4"/>
-      <x:c r="N174" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O174" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P174" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q174" s="4" t="str">
-        <x:v>5,9</x:v>
-      </x:c>
-      <x:c r="R174" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S174" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T174" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N174" s="4"/>
+      <x:c r="O174" s="5"/>
+      <x:c r="P174" s="4"/>
+      <x:c r="Q174" s="4"/>
+      <x:c r="R174" s="4"/>
+      <x:c r="S174" s="4"/>
+      <x:c r="T174" s="4"/>
       <x:c r="U174" s="9"/>
       <x:c r="V174" s="9"/>
       <x:c r="W174" s="9"/>
@@ -8114,27 +6278,13 @@
       <x:c r="K175" s="4"/>
       <x:c r="L175" s="4"/>
       <x:c r="M175" s="4"/>
-      <x:c r="N175" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O175" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P175" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q175" s="4" t="str">
-        <x:v>5,11</x:v>
-      </x:c>
-      <x:c r="R175" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S175" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T175" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N175" s="4"/>
+      <x:c r="O175" s="5"/>
+      <x:c r="P175" s="4"/>
+      <x:c r="Q175" s="4"/>
+      <x:c r="R175" s="4"/>
+      <x:c r="S175" s="4"/>
+      <x:c r="T175" s="4"/>
       <x:c r="U175" s="9"/>
       <x:c r="V175" s="9"/>
       <x:c r="W175" s="9"/>
@@ -8153,27 +6303,13 @@
       <x:c r="K176" s="4"/>
       <x:c r="L176" s="4"/>
       <x:c r="M176" s="4"/>
-      <x:c r="N176" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O176" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P176" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q176" s="4" t="str">
-        <x:v>5,13</x:v>
-      </x:c>
-      <x:c r="R176" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S176" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T176" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N176" s="4"/>
+      <x:c r="O176" s="5"/>
+      <x:c r="P176" s="4"/>
+      <x:c r="Q176" s="4"/>
+      <x:c r="R176" s="4"/>
+      <x:c r="S176" s="4"/>
+      <x:c r="T176" s="4"/>
       <x:c r="U176" s="9"/>
       <x:c r="V176" s="9"/>
       <x:c r="W176" s="9"/>
@@ -8192,27 +6328,13 @@
       <x:c r="K177" s="4"/>
       <x:c r="L177" s="4"/>
       <x:c r="M177" s="4"/>
-      <x:c r="N177" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O177" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_032</x:v>
-      </x:c>
-      <x:c r="P177" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q177" s="4" t="str">
-        <x:v>5,15</x:v>
-      </x:c>
-      <x:c r="R177" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S177" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T177" s="4" t="str">
-        <x:v>-0.25,0</x:v>
-      </x:c>
+      <x:c r="N177" s="4"/>
+      <x:c r="O177" s="5"/>
+      <x:c r="P177" s="4"/>
+      <x:c r="Q177" s="4"/>
+      <x:c r="R177" s="4"/>
+      <x:c r="S177" s="4"/>
+      <x:c r="T177" s="4"/>
       <x:c r="U177" s="9"/>
       <x:c r="V177" s="9"/>
       <x:c r="W177" s="9"/>
@@ -8231,27 +6353,13 @@
       <x:c r="K178" s="4"/>
       <x:c r="L178" s="4"/>
       <x:c r="M178" s="4"/>
-      <x:c r="N178" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O178" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P178" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q178" s="4" t="str">
-        <x:v>-5,-15</x:v>
-      </x:c>
-      <x:c r="R178" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S178" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T178" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N178" s="4"/>
+      <x:c r="O178" s="5"/>
+      <x:c r="P178" s="4"/>
+      <x:c r="Q178" s="4"/>
+      <x:c r="R178" s="4"/>
+      <x:c r="S178" s="4"/>
+      <x:c r="T178" s="4"/>
       <x:c r="U178" s="9"/>
       <x:c r="V178" s="9"/>
       <x:c r="W178" s="9"/>
@@ -8270,27 +6378,13 @@
       <x:c r="K179" s="4"/>
       <x:c r="L179" s="4"/>
       <x:c r="M179" s="4"/>
-      <x:c r="N179" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O179" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P179" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q179" s="4" t="str">
-        <x:v>-5,-13</x:v>
-      </x:c>
-      <x:c r="R179" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S179" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T179" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N179" s="4"/>
+      <x:c r="O179" s="5"/>
+      <x:c r="P179" s="4"/>
+      <x:c r="Q179" s="4"/>
+      <x:c r="R179" s="4"/>
+      <x:c r="S179" s="4"/>
+      <x:c r="T179" s="4"/>
       <x:c r="U179" s="9"/>
       <x:c r="V179" s="9"/>
       <x:c r="W179" s="9"/>
@@ -8309,27 +6403,13 @@
       <x:c r="K180" s="4"/>
       <x:c r="L180" s="4"/>
       <x:c r="M180" s="4"/>
-      <x:c r="N180" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O180" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P180" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q180" s="4" t="str">
-        <x:v>-5,-11</x:v>
-      </x:c>
-      <x:c r="R180" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S180" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T180" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N180" s="4"/>
+      <x:c r="O180" s="5"/>
+      <x:c r="P180" s="4"/>
+      <x:c r="Q180" s="4"/>
+      <x:c r="R180" s="4"/>
+      <x:c r="S180" s="4"/>
+      <x:c r="T180" s="4"/>
       <x:c r="U180" s="9"/>
       <x:c r="V180" s="9"/>
       <x:c r="W180" s="9"/>
@@ -8348,27 +6428,13 @@
       <x:c r="K181" s="4"/>
       <x:c r="L181" s="4"/>
       <x:c r="M181" s="4"/>
-      <x:c r="N181" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O181" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P181" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q181" s="4" t="str">
-        <x:v>-5,-9</x:v>
-      </x:c>
-      <x:c r="R181" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S181" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T181" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N181" s="4"/>
+      <x:c r="O181" s="5"/>
+      <x:c r="P181" s="4"/>
+      <x:c r="Q181" s="4"/>
+      <x:c r="R181" s="4"/>
+      <x:c r="S181" s="4"/>
+      <x:c r="T181" s="4"/>
       <x:c r="U181" s="9"/>
       <x:c r="V181" s="9"/>
       <x:c r="W181" s="9"/>
@@ -8387,27 +6453,13 @@
       <x:c r="K182" s="4"/>
       <x:c r="L182" s="4"/>
       <x:c r="M182" s="4"/>
-      <x:c r="N182" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O182" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P182" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q182" s="4" t="str">
-        <x:v>-5,-7</x:v>
-      </x:c>
-      <x:c r="R182" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S182" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T182" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N182" s="4"/>
+      <x:c r="O182" s="5"/>
+      <x:c r="P182" s="4"/>
+      <x:c r="Q182" s="4"/>
+      <x:c r="R182" s="4"/>
+      <x:c r="S182" s="4"/>
+      <x:c r="T182" s="4"/>
       <x:c r="U182" s="9"/>
       <x:c r="V182" s="9"/>
       <x:c r="W182" s="9"/>
@@ -8426,27 +6478,13 @@
       <x:c r="K183" s="4"/>
       <x:c r="L183" s="4"/>
       <x:c r="M183" s="4"/>
-      <x:c r="N183" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O183" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P183" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q183" s="4" t="str">
-        <x:v>-5,-5</x:v>
-      </x:c>
-      <x:c r="R183" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S183" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T183" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N183" s="4"/>
+      <x:c r="O183" s="5"/>
+      <x:c r="P183" s="4"/>
+      <x:c r="Q183" s="4"/>
+      <x:c r="R183" s="4"/>
+      <x:c r="S183" s="4"/>
+      <x:c r="T183" s="4"/>
       <x:c r="U183" s="9"/>
       <x:c r="V183" s="9"/>
       <x:c r="W183" s="9"/>
@@ -8465,27 +6503,13 @@
       <x:c r="K184" s="4"/>
       <x:c r="L184" s="4"/>
       <x:c r="M184" s="4"/>
-      <x:c r="N184" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O184" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P184" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q184" s="4" t="str">
-        <x:v>-5,-3</x:v>
-      </x:c>
-      <x:c r="R184" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S184" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T184" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N184" s="4"/>
+      <x:c r="O184" s="5"/>
+      <x:c r="P184" s="4"/>
+      <x:c r="Q184" s="4"/>
+      <x:c r="R184" s="4"/>
+      <x:c r="S184" s="4"/>
+      <x:c r="T184" s="4"/>
       <x:c r="U184" s="9"/>
       <x:c r="V184" s="9"/>
       <x:c r="W184" s="9"/>
@@ -8504,27 +6528,13 @@
       <x:c r="K185" s="4"/>
       <x:c r="L185" s="4"/>
       <x:c r="M185" s="4"/>
-      <x:c r="N185" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O185" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P185" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q185" s="4" t="str">
-        <x:v>-5,-1</x:v>
-      </x:c>
-      <x:c r="R185" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S185" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T185" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N185" s="4"/>
+      <x:c r="O185" s="5"/>
+      <x:c r="P185" s="4"/>
+      <x:c r="Q185" s="4"/>
+      <x:c r="R185" s="4"/>
+      <x:c r="S185" s="4"/>
+      <x:c r="T185" s="4"/>
       <x:c r="U185" s="9"/>
       <x:c r="V185" s="9"/>
       <x:c r="W185" s="9"/>
@@ -8543,27 +6553,13 @@
       <x:c r="K186" s="4"/>
       <x:c r="L186" s="4"/>
       <x:c r="M186" s="4"/>
-      <x:c r="N186" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O186" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P186" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q186" s="4" t="str">
-        <x:v>-5,1</x:v>
-      </x:c>
-      <x:c r="R186" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S186" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T186" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N186" s="4"/>
+      <x:c r="O186" s="5"/>
+      <x:c r="P186" s="4"/>
+      <x:c r="Q186" s="4"/>
+      <x:c r="R186" s="4"/>
+      <x:c r="S186" s="4"/>
+      <x:c r="T186" s="4"/>
       <x:c r="U186" s="9"/>
       <x:c r="V186" s="9"/>
       <x:c r="W186" s="9"/>
@@ -8582,27 +6578,13 @@
       <x:c r="K187" s="4"/>
       <x:c r="L187" s="4"/>
       <x:c r="M187" s="4"/>
-      <x:c r="N187" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O187" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P187" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q187" s="4" t="str">
-        <x:v>-5,3</x:v>
-      </x:c>
-      <x:c r="R187" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S187" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T187" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N187" s="4"/>
+      <x:c r="O187" s="5"/>
+      <x:c r="P187" s="4"/>
+      <x:c r="Q187" s="4"/>
+      <x:c r="R187" s="4"/>
+      <x:c r="S187" s="4"/>
+      <x:c r="T187" s="4"/>
       <x:c r="U187" s="9"/>
       <x:c r="V187" s="9"/>
       <x:c r="W187" s="9"/>
@@ -8621,27 +6603,13 @@
       <x:c r="K188" s="4"/>
       <x:c r="L188" s="4"/>
       <x:c r="M188" s="4"/>
-      <x:c r="N188" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O188" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P188" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q188" s="4" t="str">
-        <x:v>-5,5</x:v>
-      </x:c>
-      <x:c r="R188" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S188" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T188" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N188" s="4"/>
+      <x:c r="O188" s="5"/>
+      <x:c r="P188" s="4"/>
+      <x:c r="Q188" s="4"/>
+      <x:c r="R188" s="4"/>
+      <x:c r="S188" s="4"/>
+      <x:c r="T188" s="4"/>
       <x:c r="U188" s="9"/>
       <x:c r="V188" s="9"/>
       <x:c r="W188" s="9"/>
@@ -8660,27 +6628,13 @@
       <x:c r="K189" s="4"/>
       <x:c r="L189" s="4"/>
       <x:c r="M189" s="4"/>
-      <x:c r="N189" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O189" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P189" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q189" s="4" t="str">
-        <x:v>-5,7</x:v>
-      </x:c>
-      <x:c r="R189" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S189" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T189" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N189" s="4"/>
+      <x:c r="O189" s="5"/>
+      <x:c r="P189" s="4"/>
+      <x:c r="Q189" s="4"/>
+      <x:c r="R189" s="4"/>
+      <x:c r="S189" s="4"/>
+      <x:c r="T189" s="4"/>
       <x:c r="U189" s="9"/>
       <x:c r="V189" s="9"/>
       <x:c r="W189" s="9"/>
@@ -8699,27 +6653,13 @@
       <x:c r="K190" s="4"/>
       <x:c r="L190" s="4"/>
       <x:c r="M190" s="4"/>
-      <x:c r="N190" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O190" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P190" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q190" s="4" t="str">
-        <x:v>-5,9</x:v>
-      </x:c>
-      <x:c r="R190" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S190" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T190" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N190" s="4"/>
+      <x:c r="O190" s="5"/>
+      <x:c r="P190" s="4"/>
+      <x:c r="Q190" s="4"/>
+      <x:c r="R190" s="4"/>
+      <x:c r="S190" s="4"/>
+      <x:c r="T190" s="4"/>
       <x:c r="U190" s="9"/>
       <x:c r="V190" s="9"/>
       <x:c r="W190" s="9"/>
@@ -8738,27 +6678,13 @@
       <x:c r="K191" s="4"/>
       <x:c r="L191" s="4"/>
       <x:c r="M191" s="4"/>
-      <x:c r="N191" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O191" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P191" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q191" s="4" t="str">
-        <x:v>-5,11</x:v>
-      </x:c>
-      <x:c r="R191" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S191" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T191" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N191" s="4"/>
+      <x:c r="O191" s="5"/>
+      <x:c r="P191" s="4"/>
+      <x:c r="Q191" s="4"/>
+      <x:c r="R191" s="4"/>
+      <x:c r="S191" s="4"/>
+      <x:c r="T191" s="4"/>
       <x:c r="U191" s="9"/>
       <x:c r="V191" s="9"/>
       <x:c r="W191" s="9"/>
@@ -8777,27 +6703,13 @@
       <x:c r="K192" s="4"/>
       <x:c r="L192" s="4"/>
       <x:c r="M192" s="4"/>
-      <x:c r="N192" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O192" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P192" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q192" s="4" t="str">
-        <x:v>-5,13</x:v>
-      </x:c>
-      <x:c r="R192" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S192" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T192" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N192" s="4"/>
+      <x:c r="O192" s="5"/>
+      <x:c r="P192" s="4"/>
+      <x:c r="Q192" s="4"/>
+      <x:c r="R192" s="4"/>
+      <x:c r="S192" s="4"/>
+      <x:c r="T192" s="4"/>
       <x:c r="U192" s="9"/>
       <x:c r="V192" s="9"/>
       <x:c r="W192" s="9"/>
@@ -8816,27 +6728,13 @@
       <x:c r="K193" s="4"/>
       <x:c r="L193" s="4"/>
       <x:c r="M193" s="4"/>
-      <x:c r="N193" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O193" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P193" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q193" s="4" t="str">
-        <x:v>-5,15</x:v>
-      </x:c>
-      <x:c r="R193" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S193" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T193" s="4" t="str">
-        <x:v>40.75,39.5</x:v>
-      </x:c>
+      <x:c r="N193" s="4"/>
+      <x:c r="O193" s="5"/>
+      <x:c r="P193" s="4"/>
+      <x:c r="Q193" s="4"/>
+      <x:c r="R193" s="4"/>
+      <x:c r="S193" s="4"/>
+      <x:c r="T193" s="4"/>
       <x:c r="U193" s="9"/>
       <x:c r="V193" s="9"/>
       <x:c r="W193" s="9"/>
@@ -8855,27 +6753,13 @@
       <x:c r="K194" s="4"/>
       <x:c r="L194" s="4"/>
       <x:c r="M194" s="4"/>
-      <x:c r="N194" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O194" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P194" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q194" s="4" t="str">
-        <x:v>-5,15</x:v>
-      </x:c>
-      <x:c r="R194" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S194" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T194" s="4" t="str">
-        <x:v>0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N194" s="4"/>
+      <x:c r="O194" s="5"/>
+      <x:c r="P194" s="4"/>
+      <x:c r="Q194" s="4"/>
+      <x:c r="R194" s="4"/>
+      <x:c r="S194" s="4"/>
+      <x:c r="T194" s="4"/>
       <x:c r="U194" s="9"/>
       <x:c r="V194" s="9"/>
       <x:c r="W194" s="9"/>
@@ -8894,27 +6778,13 @@
       <x:c r="K195" s="4"/>
       <x:c r="L195" s="4"/>
       <x:c r="M195" s="4"/>
-      <x:c r="N195" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O195" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P195" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q195" s="4" t="str">
-        <x:v>-5,15</x:v>
-      </x:c>
-      <x:c r="R195" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="S195" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T195" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N195" s="4"/>
+      <x:c r="O195" s="5"/>
+      <x:c r="P195" s="4"/>
+      <x:c r="Q195" s="4"/>
+      <x:c r="R195" s="4"/>
+      <x:c r="S195" s="4"/>
+      <x:c r="T195" s="4"/>
       <x:c r="U195" s="9"/>
       <x:c r="V195" s="9"/>
       <x:c r="W195" s="9"/>
@@ -8933,27 +6803,13 @@
       <x:c r="K196" s="4"/>
       <x:c r="L196" s="4"/>
       <x:c r="M196" s="4"/>
-      <x:c r="N196" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O196" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_190</x:v>
-      </x:c>
-      <x:c r="P196" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q196" s="4" t="str">
-        <x:v>-4,14</x:v>
-      </x:c>
-      <x:c r="R196" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S196" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T196" s="4" t="str">
-        <x:v>0,63</x:v>
-      </x:c>
+      <x:c r="N196" s="4"/>
+      <x:c r="O196" s="5"/>
+      <x:c r="P196" s="4"/>
+      <x:c r="Q196" s="4"/>
+      <x:c r="R196" s="4"/>
+      <x:c r="S196" s="4"/>
+      <x:c r="T196" s="4"/>
       <x:c r="U196" s="9"/>
       <x:c r="V196" s="9"/>
       <x:c r="W196" s="9"/>
@@ -8972,27 +6828,13 @@
       <x:c r="K197" s="4"/>
       <x:c r="L197" s="4"/>
       <x:c r="M197" s="4"/>
-      <x:c r="N197" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O197" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P197" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q197" s="4" t="str">
-        <x:v>-3,15</x:v>
-      </x:c>
-      <x:c r="R197" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S197" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T197" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N197" s="4"/>
+      <x:c r="O197" s="5"/>
+      <x:c r="P197" s="4"/>
+      <x:c r="Q197" s="4"/>
+      <x:c r="R197" s="4"/>
+      <x:c r="S197" s="4"/>
+      <x:c r="T197" s="4"/>
       <x:c r="U197" s="9"/>
       <x:c r="V197" s="9"/>
       <x:c r="W197" s="9"/>
@@ -9011,27 +6853,13 @@
       <x:c r="K198" s="4"/>
       <x:c r="L198" s="4"/>
       <x:c r="M198" s="4"/>
-      <x:c r="N198" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O198" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P198" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q198" s="4" t="str">
-        <x:v>-3,15</x:v>
-      </x:c>
-      <x:c r="R198" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S198" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T198" s="4" t="str">
-        <x:v>-0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N198" s="4"/>
+      <x:c r="O198" s="5"/>
+      <x:c r="P198" s="4"/>
+      <x:c r="Q198" s="4"/>
+      <x:c r="R198" s="4"/>
+      <x:c r="S198" s="4"/>
+      <x:c r="T198" s="4"/>
       <x:c r="U198" s="9"/>
       <x:c r="V198" s="9"/>
       <x:c r="W198" s="9"/>
@@ -9050,27 +6878,13 @@
       <x:c r="K199" s="4"/>
       <x:c r="L199" s="4"/>
       <x:c r="M199" s="4"/>
-      <x:c r="N199" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O199" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P199" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q199" s="4" t="str">
-        <x:v>-3,15</x:v>
-      </x:c>
-      <x:c r="R199" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="S199" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T199" s="4" t="str">
-        <x:v>-40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N199" s="4"/>
+      <x:c r="O199" s="5"/>
+      <x:c r="P199" s="4"/>
+      <x:c r="Q199" s="4"/>
+      <x:c r="R199" s="4"/>
+      <x:c r="S199" s="4"/>
+      <x:c r="T199" s="4"/>
       <x:c r="U199" s="9"/>
       <x:c r="V199" s="9"/>
       <x:c r="W199" s="9"/>
@@ -9089,27 +6903,13 @@
       <x:c r="K200" s="4"/>
       <x:c r="L200" s="4"/>
       <x:c r="M200" s="4"/>
-      <x:c r="N200" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O200" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_194</x:v>
-      </x:c>
-      <x:c r="P200" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q200" s="4" t="str">
-        <x:v>-2,14</x:v>
-      </x:c>
-      <x:c r="R200" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S200" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T200" s="4" t="str">
-        <x:v>0,63</x:v>
-      </x:c>
+      <x:c r="N200" s="4"/>
+      <x:c r="O200" s="5"/>
+      <x:c r="P200" s="4"/>
+      <x:c r="Q200" s="4"/>
+      <x:c r="R200" s="4"/>
+      <x:c r="S200" s="4"/>
+      <x:c r="T200" s="4"/>
       <x:c r="U200" s="9"/>
       <x:c r="V200" s="9"/>
       <x:c r="W200" s="9"/>
@@ -9128,27 +6928,13 @@
       <x:c r="K201" s="4"/>
       <x:c r="L201" s="4"/>
       <x:c r="M201" s="4"/>
-      <x:c r="N201" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O201" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P201" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q201" s="4" t="str">
-        <x:v>-1,15</x:v>
-      </x:c>
-      <x:c r="R201" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S201" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T201" s="4" t="str">
-        <x:v>40.75,39.5</x:v>
-      </x:c>
+      <x:c r="N201" s="4"/>
+      <x:c r="O201" s="5"/>
+      <x:c r="P201" s="4"/>
+      <x:c r="Q201" s="4"/>
+      <x:c r="R201" s="4"/>
+      <x:c r="S201" s="4"/>
+      <x:c r="T201" s="4"/>
       <x:c r="U201" s="9"/>
       <x:c r="V201" s="9"/>
       <x:c r="W201" s="9"/>
@@ -9167,27 +6953,13 @@
       <x:c r="K202" s="4"/>
       <x:c r="L202" s="4"/>
       <x:c r="M202" s="4"/>
-      <x:c r="N202" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O202" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P202" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q202" s="4" t="str">
-        <x:v>-1,15</x:v>
-      </x:c>
-      <x:c r="R202" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S202" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T202" s="4" t="str">
-        <x:v>0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N202" s="4"/>
+      <x:c r="O202" s="5"/>
+      <x:c r="P202" s="4"/>
+      <x:c r="Q202" s="4"/>
+      <x:c r="R202" s="4"/>
+      <x:c r="S202" s="4"/>
+      <x:c r="T202" s="4"/>
       <x:c r="U202" s="9"/>
       <x:c r="V202" s="9"/>
       <x:c r="W202" s="9"/>
@@ -9206,27 +6978,13 @@
       <x:c r="K203" s="4"/>
       <x:c r="L203" s="4"/>
       <x:c r="M203" s="4"/>
-      <x:c r="N203" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O203" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P203" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q203" s="4" t="str">
-        <x:v>-1,15</x:v>
-      </x:c>
-      <x:c r="R203" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S203" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T203" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N203" s="4"/>
+      <x:c r="O203" s="5"/>
+      <x:c r="P203" s="4"/>
+      <x:c r="Q203" s="4"/>
+      <x:c r="R203" s="4"/>
+      <x:c r="S203" s="4"/>
+      <x:c r="T203" s="4"/>
       <x:c r="U203" s="9"/>
       <x:c r="V203" s="9"/>
       <x:c r="W203" s="9"/>
@@ -9245,27 +7003,13 @@
       <x:c r="K204" s="4"/>
       <x:c r="L204" s="4"/>
       <x:c r="M204" s="4"/>
-      <x:c r="N204" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O204" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_190</x:v>
-      </x:c>
-      <x:c r="P204" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q204" s="4" t="str">
-        <x:v>0,14</x:v>
-      </x:c>
-      <x:c r="R204" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S204" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T204" s="4" t="str">
-        <x:v>0,63</x:v>
-      </x:c>
+      <x:c r="N204" s="4"/>
+      <x:c r="O204" s="5"/>
+      <x:c r="P204" s="4"/>
+      <x:c r="Q204" s="4"/>
+      <x:c r="R204" s="4"/>
+      <x:c r="S204" s="4"/>
+      <x:c r="T204" s="4"/>
       <x:c r="U204" s="9"/>
       <x:c r="V204" s="9"/>
       <x:c r="W204" s="9"/>
@@ -9284,27 +7028,13 @@
       <x:c r="K205" s="4"/>
       <x:c r="L205" s="4"/>
       <x:c r="M205" s="4"/>
-      <x:c r="N205" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O205" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P205" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q205" s="4" t="str">
-        <x:v>1,15</x:v>
-      </x:c>
-      <x:c r="R205" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S205" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T205" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N205" s="4"/>
+      <x:c r="O205" s="5"/>
+      <x:c r="P205" s="4"/>
+      <x:c r="Q205" s="4"/>
+      <x:c r="R205" s="4"/>
+      <x:c r="S205" s="4"/>
+      <x:c r="T205" s="4"/>
       <x:c r="U205" s="9"/>
       <x:c r="V205" s="9"/>
       <x:c r="W205" s="9"/>
@@ -9323,27 +7053,13 @@
       <x:c r="K206" s="4"/>
       <x:c r="L206" s="4"/>
       <x:c r="M206" s="4"/>
-      <x:c r="N206" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O206" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P206" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q206" s="4" t="str">
-        <x:v>1,15</x:v>
-      </x:c>
-      <x:c r="R206" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S206" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T206" s="4" t="str">
-        <x:v>-0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N206" s="4"/>
+      <x:c r="O206" s="5"/>
+      <x:c r="P206" s="4"/>
+      <x:c r="Q206" s="4"/>
+      <x:c r="R206" s="4"/>
+      <x:c r="S206" s="4"/>
+      <x:c r="T206" s="4"/>
       <x:c r="U206" s="9"/>
       <x:c r="V206" s="9"/>
       <x:c r="W206" s="9"/>
@@ -9362,27 +7078,13 @@
       <x:c r="K207" s="4"/>
       <x:c r="L207" s="4"/>
       <x:c r="M207" s="4"/>
-      <x:c r="N207" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O207" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P207" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q207" s="4" t="str">
-        <x:v>1,15</x:v>
-      </x:c>
-      <x:c r="R207" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S207" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T207" s="4" t="str">
-        <x:v>-40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N207" s="4"/>
+      <x:c r="O207" s="5"/>
+      <x:c r="P207" s="4"/>
+      <x:c r="Q207" s="4"/>
+      <x:c r="R207" s="4"/>
+      <x:c r="S207" s="4"/>
+      <x:c r="T207" s="4"/>
       <x:c r="U207" s="9"/>
       <x:c r="V207" s="9"/>
       <x:c r="W207" s="9"/>
@@ -9401,27 +7103,13 @@
       <x:c r="K208" s="4"/>
       <x:c r="L208" s="4"/>
       <x:c r="M208" s="4"/>
-      <x:c r="N208" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O208" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_194</x:v>
-      </x:c>
-      <x:c r="P208" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q208" s="4" t="str">
-        <x:v>2,14</x:v>
-      </x:c>
-      <x:c r="R208" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S208" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T208" s="4" t="str">
-        <x:v>0,63</x:v>
-      </x:c>
+      <x:c r="N208" s="4"/>
+      <x:c r="O208" s="5"/>
+      <x:c r="P208" s="4"/>
+      <x:c r="Q208" s="4"/>
+      <x:c r="R208" s="4"/>
+      <x:c r="S208" s="4"/>
+      <x:c r="T208" s="4"/>
       <x:c r="U208" s="9"/>
       <x:c r="V208" s="9"/>
       <x:c r="W208" s="9"/>
@@ -9440,27 +7128,13 @@
       <x:c r="K209" s="4"/>
       <x:c r="L209" s="4"/>
       <x:c r="M209" s="4"/>
-      <x:c r="N209" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O209" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P209" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q209" s="4" t="str">
-        <x:v>3,15</x:v>
-      </x:c>
-      <x:c r="R209" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S209" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T209" s="4" t="str">
-        <x:v>40.75,39.5</x:v>
-      </x:c>
+      <x:c r="N209" s="4"/>
+      <x:c r="O209" s="5"/>
+      <x:c r="P209" s="4"/>
+      <x:c r="Q209" s="4"/>
+      <x:c r="R209" s="4"/>
+      <x:c r="S209" s="4"/>
+      <x:c r="T209" s="4"/>
       <x:c r="U209" s="9"/>
       <x:c r="V209" s="9"/>
       <x:c r="W209" s="9"/>
@@ -9479,27 +7153,13 @@
       <x:c r="K210" s="4"/>
       <x:c r="L210" s="4"/>
       <x:c r="M210" s="4"/>
-      <x:c r="N210" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O210" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P210" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q210" s="4" t="str">
-        <x:v>3,15</x:v>
-      </x:c>
-      <x:c r="R210" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S210" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T210" s="4" t="str">
-        <x:v>0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N210" s="4"/>
+      <x:c r="O210" s="5"/>
+      <x:c r="P210" s="4"/>
+      <x:c r="Q210" s="4"/>
+      <x:c r="R210" s="4"/>
+      <x:c r="S210" s="4"/>
+      <x:c r="T210" s="4"/>
       <x:c r="U210" s="9"/>
       <x:c r="V210" s="9"/>
       <x:c r="W210" s="9"/>
@@ -9518,27 +7178,13 @@
       <x:c r="K211" s="4"/>
       <x:c r="L211" s="4"/>
       <x:c r="M211" s="4"/>
-      <x:c r="N211" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O211" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P211" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q211" s="4" t="str">
-        <x:v>3,15</x:v>
-      </x:c>
-      <x:c r="R211" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S211" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T211" s="4" t="str">
-        <x:v>-39.75,39.5</x:v>
-      </x:c>
+      <x:c r="N211" s="4"/>
+      <x:c r="O211" s="5"/>
+      <x:c r="P211" s="4"/>
+      <x:c r="Q211" s="4"/>
+      <x:c r="R211" s="4"/>
+      <x:c r="S211" s="4"/>
+      <x:c r="T211" s="4"/>
       <x:c r="U211" s="9"/>
       <x:c r="V211" s="9"/>
       <x:c r="W211" s="9"/>
@@ -9557,27 +7203,13 @@
       <x:c r="K212" s="4"/>
       <x:c r="L212" s="4"/>
       <x:c r="M212" s="4"/>
-      <x:c r="N212" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O212" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_190</x:v>
-      </x:c>
-      <x:c r="P212" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q212" s="4" t="str">
-        <x:v>4,14</x:v>
-      </x:c>
-      <x:c r="R212" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S212" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T212" s="4" t="str">
-        <x:v>0,63</x:v>
-      </x:c>
+      <x:c r="N212" s="4"/>
+      <x:c r="O212" s="5"/>
+      <x:c r="P212" s="4"/>
+      <x:c r="Q212" s="4"/>
+      <x:c r="R212" s="4"/>
+      <x:c r="S212" s="4"/>
+      <x:c r="T212" s="4"/>
       <x:c r="U212" s="9"/>
       <x:c r="V212" s="9"/>
       <x:c r="W212" s="9"/>
@@ -9596,27 +7228,13 @@
       <x:c r="K213" s="4"/>
       <x:c r="L213" s="4"/>
       <x:c r="M213" s="4"/>
-      <x:c r="N213" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O213" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P213" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q213" s="4" t="str">
-        <x:v>5,-15</x:v>
-      </x:c>
-      <x:c r="R213" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S213" s="4" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="T213" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N213" s="4"/>
+      <x:c r="O213" s="5"/>
+      <x:c r="P213" s="4"/>
+      <x:c r="Q213" s="4"/>
+      <x:c r="R213" s="4"/>
+      <x:c r="S213" s="4"/>
+      <x:c r="T213" s="4"/>
       <x:c r="U213" s="9"/>
       <x:c r="V213" s="9"/>
       <x:c r="W213" s="9"/>
@@ -9635,27 +7253,13 @@
       <x:c r="K214" s="4"/>
       <x:c r="L214" s="4"/>
       <x:c r="M214" s="4"/>
-      <x:c r="N214" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O214" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P214" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q214" s="4" t="str">
-        <x:v>5,-13</x:v>
-      </x:c>
-      <x:c r="R214" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S214" s="4" t="n">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="T214" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N214" s="4"/>
+      <x:c r="O214" s="5"/>
+      <x:c r="P214" s="4"/>
+      <x:c r="Q214" s="4"/>
+      <x:c r="R214" s="4"/>
+      <x:c r="S214" s="4"/>
+      <x:c r="T214" s="4"/>
       <x:c r="U214" s="9"/>
       <x:c r="V214" s="9"/>
       <x:c r="W214" s="9"/>
@@ -9674,27 +7278,13 @@
       <x:c r="K215" s="4"/>
       <x:c r="L215" s="4"/>
       <x:c r="M215" s="4"/>
-      <x:c r="N215" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O215" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P215" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q215" s="4" t="str">
-        <x:v>5,-11</x:v>
-      </x:c>
-      <x:c r="R215" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S215" s="4" t="n">
-        <x:v>-11</x:v>
-      </x:c>
-      <x:c r="T215" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N215" s="4"/>
+      <x:c r="O215" s="5"/>
+      <x:c r="P215" s="4"/>
+      <x:c r="Q215" s="4"/>
+      <x:c r="R215" s="4"/>
+      <x:c r="S215" s="4"/>
+      <x:c r="T215" s="4"/>
       <x:c r="U215" s="9"/>
       <x:c r="V215" s="9"/>
       <x:c r="W215" s="9"/>
@@ -9713,27 +7303,13 @@
       <x:c r="K216" s="4"/>
       <x:c r="L216" s="4"/>
       <x:c r="M216" s="4"/>
-      <x:c r="N216" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O216" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P216" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q216" s="4" t="str">
-        <x:v>5,-9</x:v>
-      </x:c>
-      <x:c r="R216" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S216" s="4" t="n">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="T216" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N216" s="4"/>
+      <x:c r="O216" s="5"/>
+      <x:c r="P216" s="4"/>
+      <x:c r="Q216" s="4"/>
+      <x:c r="R216" s="4"/>
+      <x:c r="S216" s="4"/>
+      <x:c r="T216" s="4"/>
       <x:c r="U216" s="9"/>
       <x:c r="V216" s="9"/>
       <x:c r="W216" s="9"/>
@@ -9752,27 +7328,13 @@
       <x:c r="K217" s="4"/>
       <x:c r="L217" s="4"/>
       <x:c r="M217" s="4"/>
-      <x:c r="N217" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O217" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P217" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q217" s="4" t="str">
-        <x:v>5,-7</x:v>
-      </x:c>
-      <x:c r="R217" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S217" s="4" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="T217" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N217" s="4"/>
+      <x:c r="O217" s="5"/>
+      <x:c r="P217" s="4"/>
+      <x:c r="Q217" s="4"/>
+      <x:c r="R217" s="4"/>
+      <x:c r="S217" s="4"/>
+      <x:c r="T217" s="4"/>
       <x:c r="U217" s="9"/>
       <x:c r="V217" s="9"/>
       <x:c r="W217" s="9"/>
@@ -9791,27 +7353,13 @@
       <x:c r="K218" s="4"/>
       <x:c r="L218" s="4"/>
       <x:c r="M218" s="4"/>
-      <x:c r="N218" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O218" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P218" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q218" s="4" t="str">
-        <x:v>5,-5</x:v>
-      </x:c>
-      <x:c r="R218" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S218" s="4" t="n">
-        <x:v>-5</x:v>
-      </x:c>
-      <x:c r="T218" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N218" s="4"/>
+      <x:c r="O218" s="5"/>
+      <x:c r="P218" s="4"/>
+      <x:c r="Q218" s="4"/>
+      <x:c r="R218" s="4"/>
+      <x:c r="S218" s="4"/>
+      <x:c r="T218" s="4"/>
       <x:c r="U218" s="9"/>
       <x:c r="V218" s="9"/>
       <x:c r="W218" s="9"/>
@@ -9830,27 +7378,13 @@
       <x:c r="K219" s="4"/>
       <x:c r="L219" s="4"/>
       <x:c r="M219" s="4"/>
-      <x:c r="N219" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O219" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P219" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q219" s="4" t="str">
-        <x:v>5,-3</x:v>
-      </x:c>
-      <x:c r="R219" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S219" s="4" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="T219" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N219" s="4"/>
+      <x:c r="O219" s="5"/>
+      <x:c r="P219" s="4"/>
+      <x:c r="Q219" s="4"/>
+      <x:c r="R219" s="4"/>
+      <x:c r="S219" s="4"/>
+      <x:c r="T219" s="4"/>
       <x:c r="U219" s="9"/>
       <x:c r="V219" s="9"/>
       <x:c r="W219" s="9"/>
@@ -9869,27 +7403,13 @@
       <x:c r="K220" s="4"/>
       <x:c r="L220" s="4"/>
       <x:c r="M220" s="4"/>
-      <x:c r="N220" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O220" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P220" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q220" s="4" t="str">
-        <x:v>5,-1</x:v>
-      </x:c>
-      <x:c r="R220" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S220" s="4" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="T220" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N220" s="4"/>
+      <x:c r="O220" s="5"/>
+      <x:c r="P220" s="4"/>
+      <x:c r="Q220" s="4"/>
+      <x:c r="R220" s="4"/>
+      <x:c r="S220" s="4"/>
+      <x:c r="T220" s="4"/>
       <x:c r="U220" s="9"/>
       <x:c r="V220" s="9"/>
       <x:c r="W220" s="9"/>
@@ -9908,27 +7428,13 @@
       <x:c r="K221" s="4"/>
       <x:c r="L221" s="4"/>
       <x:c r="M221" s="4"/>
-      <x:c r="N221" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O221" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P221" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q221" s="4" t="str">
-        <x:v>5,1</x:v>
-      </x:c>
-      <x:c r="R221" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S221" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T221" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N221" s="4"/>
+      <x:c r="O221" s="5"/>
+      <x:c r="P221" s="4"/>
+      <x:c r="Q221" s="4"/>
+      <x:c r="R221" s="4"/>
+      <x:c r="S221" s="4"/>
+      <x:c r="T221" s="4"/>
       <x:c r="U221" s="9"/>
       <x:c r="V221" s="9"/>
       <x:c r="W221" s="9"/>
@@ -9947,27 +7453,13 @@
       <x:c r="K222" s="4"/>
       <x:c r="L222" s="4"/>
       <x:c r="M222" s="4"/>
-      <x:c r="N222" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O222" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P222" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q222" s="4" t="str">
-        <x:v>5,3</x:v>
-      </x:c>
-      <x:c r="R222" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S222" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T222" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N222" s="4"/>
+      <x:c r="O222" s="5"/>
+      <x:c r="P222" s="4"/>
+      <x:c r="Q222" s="4"/>
+      <x:c r="R222" s="4"/>
+      <x:c r="S222" s="4"/>
+      <x:c r="T222" s="4"/>
       <x:c r="U222" s="9"/>
       <x:c r="V222" s="9"/>
       <x:c r="W222" s="9"/>
@@ -9986,27 +7478,13 @@
       <x:c r="K223" s="4"/>
       <x:c r="L223" s="4"/>
       <x:c r="M223" s="4"/>
-      <x:c r="N223" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O223" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P223" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q223" s="4" t="str">
-        <x:v>5,5</x:v>
-      </x:c>
-      <x:c r="R223" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S223" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T223" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N223" s="4"/>
+      <x:c r="O223" s="5"/>
+      <x:c r="P223" s="4"/>
+      <x:c r="Q223" s="4"/>
+      <x:c r="R223" s="4"/>
+      <x:c r="S223" s="4"/>
+      <x:c r="T223" s="4"/>
       <x:c r="U223" s="9"/>
       <x:c r="V223" s="9"/>
       <x:c r="W223" s="9"/>
@@ -10025,27 +7503,13 @@
       <x:c r="K224" s="4"/>
       <x:c r="L224" s="4"/>
       <x:c r="M224" s="4"/>
-      <x:c r="N224" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O224" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P224" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q224" s="4" t="str">
-        <x:v>5,7</x:v>
-      </x:c>
-      <x:c r="R224" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S224" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T224" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N224" s="4"/>
+      <x:c r="O224" s="5"/>
+      <x:c r="P224" s="4"/>
+      <x:c r="Q224" s="4"/>
+      <x:c r="R224" s="4"/>
+      <x:c r="S224" s="4"/>
+      <x:c r="T224" s="4"/>
       <x:c r="U224" s="9"/>
       <x:c r="V224" s="9"/>
       <x:c r="W224" s="9"/>
@@ -10064,27 +7528,13 @@
       <x:c r="K225" s="4"/>
       <x:c r="L225" s="4"/>
       <x:c r="M225" s="4"/>
-      <x:c r="N225" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O225" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P225" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q225" s="4" t="str">
-        <x:v>5,9</x:v>
-      </x:c>
-      <x:c r="R225" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S225" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T225" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N225" s="4"/>
+      <x:c r="O225" s="5"/>
+      <x:c r="P225" s="4"/>
+      <x:c r="Q225" s="4"/>
+      <x:c r="R225" s="4"/>
+      <x:c r="S225" s="4"/>
+      <x:c r="T225" s="4"/>
       <x:c r="U225" s="9"/>
       <x:c r="V225" s="9"/>
       <x:c r="W225" s="9"/>
@@ -10103,27 +7553,13 @@
       <x:c r="K226" s="4"/>
       <x:c r="L226" s="4"/>
       <x:c r="M226" s="4"/>
-      <x:c r="N226" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O226" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P226" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q226" s="4" t="str">
-        <x:v>5,11</x:v>
-      </x:c>
-      <x:c r="R226" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S226" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T226" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N226" s="4"/>
+      <x:c r="O226" s="5"/>
+      <x:c r="P226" s="4"/>
+      <x:c r="Q226" s="4"/>
+      <x:c r="R226" s="4"/>
+      <x:c r="S226" s="4"/>
+      <x:c r="T226" s="4"/>
       <x:c r="U226" s="9"/>
       <x:c r="V226" s="9"/>
       <x:c r="W226" s="9"/>
@@ -10142,27 +7578,13 @@
       <x:c r="K227" s="4"/>
       <x:c r="L227" s="4"/>
       <x:c r="M227" s="4"/>
-      <x:c r="N227" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O227" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P227" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q227" s="4" t="str">
-        <x:v>5,13</x:v>
-      </x:c>
-      <x:c r="R227" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S227" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T227" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N227" s="4"/>
+      <x:c r="O227" s="5"/>
+      <x:c r="P227" s="4"/>
+      <x:c r="Q227" s="4"/>
+      <x:c r="R227" s="4"/>
+      <x:c r="S227" s="4"/>
+      <x:c r="T227" s="4"/>
       <x:c r="U227" s="9"/>
       <x:c r="V227" s="9"/>
       <x:c r="W227" s="9"/>
@@ -10181,27 +7603,13 @@
       <x:c r="K228" s="4"/>
       <x:c r="L228" s="4"/>
       <x:c r="M228" s="4"/>
-      <x:c r="N228" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O228" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_187</x:v>
-      </x:c>
-      <x:c r="P228" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q228" s="4" t="str">
-        <x:v>5,15</x:v>
-      </x:c>
-      <x:c r="R228" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S228" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T228" s="4" t="str">
-        <x:v>40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N228" s="4"/>
+      <x:c r="O228" s="5"/>
+      <x:c r="P228" s="4"/>
+      <x:c r="Q228" s="4"/>
+      <x:c r="R228" s="4"/>
+      <x:c r="S228" s="4"/>
+      <x:c r="T228" s="4"/>
       <x:c r="U228" s="9"/>
       <x:c r="V228" s="9"/>
       <x:c r="W228" s="9"/>
@@ -10220,27 +7628,13 @@
       <x:c r="K229" s="4"/>
       <x:c r="L229" s="4"/>
       <x:c r="M229" s="4"/>
-      <x:c r="N229" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O229" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_188</x:v>
-      </x:c>
-      <x:c r="P229" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q229" s="4" t="str">
-        <x:v>5,15</x:v>
-      </x:c>
-      <x:c r="R229" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S229" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T229" s="4" t="str">
-        <x:v>-0.25,62.5</x:v>
-      </x:c>
+      <x:c r="N229" s="4"/>
+      <x:c r="O229" s="5"/>
+      <x:c r="P229" s="4"/>
+      <x:c r="Q229" s="4"/>
+      <x:c r="R229" s="4"/>
+      <x:c r="S229" s="4"/>
+      <x:c r="T229" s="4"/>
       <x:c r="U229" s="9"/>
       <x:c r="V229" s="9"/>
       <x:c r="W229" s="9"/>
@@ -10259,27 +7653,13 @@
       <x:c r="K230" s="4"/>
       <x:c r="L230" s="4"/>
       <x:c r="M230" s="4"/>
-      <x:c r="N230" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O230" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_BelowGround_172</x:v>
-      </x:c>
-      <x:c r="P230" s="4" t="str">
-        <x:v>低于地面</x:v>
-      </x:c>
-      <x:c r="Q230" s="4" t="str">
-        <x:v>5,15</x:v>
-      </x:c>
-      <x:c r="R230" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S230" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T230" s="4" t="str">
-        <x:v>-40.25,39.5</x:v>
-      </x:c>
+      <x:c r="N230" s="4"/>
+      <x:c r="O230" s="5"/>
+      <x:c r="P230" s="4"/>
+      <x:c r="Q230" s="4"/>
+      <x:c r="R230" s="4"/>
+      <x:c r="S230" s="4"/>
+      <x:c r="T230" s="4"/>
       <x:c r="U230" s="9"/>
       <x:c r="V230" s="9"/>
       <x:c r="W230" s="9"/>
@@ -10298,27 +7678,13 @@
       <x:c r="K231" s="4"/>
       <x:c r="L231" s="4"/>
       <x:c r="M231" s="4"/>
-      <x:c r="N231" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O231" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_565</x:v>
-      </x:c>
-      <x:c r="P231" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q231" s="4" t="str">
-        <x:v>-4,-10</x:v>
-      </x:c>
-      <x:c r="R231" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S231" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T231" s="4" t="str">
-        <x:v>0,-3.5</x:v>
-      </x:c>
+      <x:c r="N231" s="4"/>
+      <x:c r="O231" s="5"/>
+      <x:c r="P231" s="4"/>
+      <x:c r="Q231" s="4"/>
+      <x:c r="R231" s="4"/>
+      <x:c r="S231" s="4"/>
+      <x:c r="T231" s="4"/>
       <x:c r="U231" s="9"/>
       <x:c r="V231" s="9"/>
       <x:c r="W231" s="9"/>
@@ -10337,27 +7703,13 @@
       <x:c r="K232" s="4"/>
       <x:c r="L232" s="4"/>
       <x:c r="M232" s="4"/>
-      <x:c r="N232" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O232" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_566</x:v>
-      </x:c>
-      <x:c r="P232" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q232" s="4" t="str">
-        <x:v>2,-10</x:v>
-      </x:c>
-      <x:c r="R232" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S232" s="4" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="T232" s="4" t="str">
-        <x:v>0,-13</x:v>
-      </x:c>
+      <x:c r="N232" s="4"/>
+      <x:c r="O232" s="5"/>
+      <x:c r="P232" s="4"/>
+      <x:c r="Q232" s="4"/>
+      <x:c r="R232" s="4"/>
+      <x:c r="S232" s="4"/>
+      <x:c r="T232" s="4"/>
       <x:c r="U232" s="9"/>
       <x:c r="V232" s="9"/>
       <x:c r="W232" s="9"/>
@@ -10376,27 +7728,13 @@
       <x:c r="K233" s="4"/>
       <x:c r="L233" s="4"/>
       <x:c r="M233" s="4"/>
-      <x:c r="N233" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O233" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_567</x:v>
-      </x:c>
-      <x:c r="P233" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q233" s="4" t="str">
-        <x:v>0,-6</x:v>
-      </x:c>
-      <x:c r="R233" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S233" s="4" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="T233" s="4" t="str">
-        <x:v>-0.5,11</x:v>
-      </x:c>
+      <x:c r="N233" s="4"/>
+      <x:c r="O233" s="5"/>
+      <x:c r="P233" s="4"/>
+      <x:c r="Q233" s="4"/>
+      <x:c r="R233" s="4"/>
+      <x:c r="S233" s="4"/>
+      <x:c r="T233" s="4"/>
       <x:c r="U233" s="9"/>
       <x:c r="V233" s="9"/>
       <x:c r="W233" s="9"/>
@@ -10415,27 +7753,13 @@
       <x:c r="K234" s="4"/>
       <x:c r="L234" s="4"/>
       <x:c r="M234" s="4"/>
-      <x:c r="N234" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O234" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_567</x:v>
-      </x:c>
-      <x:c r="P234" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q234" s="4" t="str">
-        <x:v>4,-4</x:v>
-      </x:c>
-      <x:c r="R234" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S234" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="T234" s="4" t="str">
-        <x:v>-0.5,11</x:v>
-      </x:c>
+      <x:c r="N234" s="4"/>
+      <x:c r="O234" s="5"/>
+      <x:c r="P234" s="4"/>
+      <x:c r="Q234" s="4"/>
+      <x:c r="R234" s="4"/>
+      <x:c r="S234" s="4"/>
+      <x:c r="T234" s="4"/>
       <x:c r="U234" s="9"/>
       <x:c r="V234" s="9"/>
       <x:c r="W234" s="9"/>
@@ -10454,27 +7778,13 @@
       <x:c r="K235" s="4"/>
       <x:c r="L235" s="4"/>
       <x:c r="M235" s="4"/>
-      <x:c r="N235" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O235" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_567</x:v>
-      </x:c>
-      <x:c r="P235" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q235" s="4" t="str">
-        <x:v>-4,4</x:v>
-      </x:c>
-      <x:c r="R235" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="S235" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T235" s="4" t="str">
-        <x:v>-0.5,11</x:v>
-      </x:c>
+      <x:c r="N235" s="4"/>
+      <x:c r="O235" s="5"/>
+      <x:c r="P235" s="4"/>
+      <x:c r="Q235" s="4"/>
+      <x:c r="R235" s="4"/>
+      <x:c r="S235" s="4"/>
+      <x:c r="T235" s="4"/>
       <x:c r="U235" s="9"/>
       <x:c r="V235" s="9"/>
       <x:c r="W235" s="9"/>
@@ -10493,27 +7803,13 @@
       <x:c r="K236" s="4"/>
       <x:c r="L236" s="4"/>
       <x:c r="M236" s="4"/>
-      <x:c r="N236" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O236" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_567</x:v>
-      </x:c>
-      <x:c r="P236" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q236" s="4" t="str">
-        <x:v>0,6</x:v>
-      </x:c>
-      <x:c r="R236" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S236" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T236" s="4" t="str">
-        <x:v>-0.5,11</x:v>
-      </x:c>
+      <x:c r="N236" s="4"/>
+      <x:c r="O236" s="5"/>
+      <x:c r="P236" s="4"/>
+      <x:c r="Q236" s="4"/>
+      <x:c r="R236" s="4"/>
+      <x:c r="S236" s="4"/>
+      <x:c r="T236" s="4"/>
       <x:c r="U236" s="9"/>
       <x:c r="V236" s="9"/>
       <x:c r="W236" s="9"/>
@@ -10532,27 +7828,13 @@
       <x:c r="K237" s="4"/>
       <x:c r="L237" s="4"/>
       <x:c r="M237" s="4"/>
-      <x:c r="N237" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O237" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_566</x:v>
-      </x:c>
-      <x:c r="P237" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q237" s="4" t="str">
-        <x:v>-2,10</x:v>
-      </x:c>
-      <x:c r="R237" s="4" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="S237" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T237" s="4" t="str">
-        <x:v>0,-13</x:v>
-      </x:c>
+      <x:c r="N237" s="4"/>
+      <x:c r="O237" s="5"/>
+      <x:c r="P237" s="4"/>
+      <x:c r="Q237" s="4"/>
+      <x:c r="R237" s="4"/>
+      <x:c r="S237" s="4"/>
+      <x:c r="T237" s="4"/>
       <x:c r="U237" s="9"/>
       <x:c r="V237" s="9"/>
       <x:c r="W237" s="9"/>
@@ -10571,27 +7853,13 @@
       <x:c r="K238" s="4"/>
       <x:c r="L238" s="4"/>
       <x:c r="M238" s="4"/>
-      <x:c r="N238" s="4" t="str">
-        <x:v>静态图片</x:v>
-      </x:c>
-      <x:c r="O238" s="5" t="str">
-        <x:v>scene/battle/appearance/Terrain_AboveGround_565</x:v>
-      </x:c>
-      <x:c r="P238" s="4" t="str">
-        <x:v>高于地面</x:v>
-      </x:c>
-      <x:c r="Q238" s="4" t="str">
-        <x:v>4,10</x:v>
-      </x:c>
-      <x:c r="R238" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S238" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T238" s="4" t="str">
-        <x:v>0,-3.5</x:v>
-      </x:c>
+      <x:c r="N238" s="4"/>
+      <x:c r="O238" s="5"/>
+      <x:c r="P238" s="4"/>
+      <x:c r="Q238" s="4"/>
+      <x:c r="R238" s="4"/>
+      <x:c r="S238" s="4"/>
+      <x:c r="T238" s="4"/>
       <x:c r="U238" s="9"/>
       <x:c r="V238" s="9"/>
       <x:c r="W238" s="9"/>
@@ -13990,21 +11258,29 @@
     <x:mergeCell ref="N2:T2"/>
     <x:mergeCell ref="N3:T3"/>
     <x:mergeCell ref="R4:S4"/>
-    <x:mergeCell ref="B7:B238"/>
-    <x:mergeCell ref="C7:C238"/>
-    <x:mergeCell ref="D7:D238"/>
-    <x:mergeCell ref="E7:E238"/>
-    <x:mergeCell ref="F7:F238"/>
-    <x:mergeCell ref="G7:G238"/>
-    <x:mergeCell ref="H7:H238"/>
-    <x:mergeCell ref="I7:I238"/>
-    <x:mergeCell ref="J7:J238"/>
-    <x:mergeCell ref="K7:K238"/>
-    <x:mergeCell ref="L7:L238"/>
-    <x:mergeCell ref="M7:M238"/>
-    <x:mergeCell ref="U7:U238"/>
-    <x:mergeCell ref="V7:V238"/>
-    <x:mergeCell ref="W7:W238"/>
+    <x:mergeCell ref="B7:B19"/>
+    <x:mergeCell ref="C7:C19"/>
+    <x:mergeCell ref="D7:D19"/>
+    <x:mergeCell ref="E7:E19"/>
+    <x:mergeCell ref="F7:F19"/>
+    <x:mergeCell ref="G7:G19"/>
+    <x:mergeCell ref="H7:H19"/>
+    <x:mergeCell ref="I7:I19"/>
+    <x:mergeCell ref="J7:J19"/>
+    <x:mergeCell ref="K7:K19"/>
+    <x:mergeCell ref="L7:L19"/>
+    <x:mergeCell ref="M7:M19"/>
+    <x:mergeCell ref="U7:U19"/>
+    <x:mergeCell ref="V7:V19"/>
+    <x:mergeCell ref="W7:W19"/>
+    <x:mergeCell ref="X7:X19"/>
+    <x:mergeCell ref="Y7:Y19"/>
+    <x:mergeCell ref="Z7:Z19"/>
+    <x:mergeCell ref="AA7:AA19"/>
+    <x:mergeCell ref="AB7:AB19"/>
+    <x:mergeCell ref="AC7:AC19"/>
+    <x:mergeCell ref="AD7:AD19"/>
+    <x:mergeCell ref="AE7:AE19"/>
   </x:mergeCells>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="N7:N10000">
@@ -14015,5 +11291,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b6e6361d00e4c25"/>
 </x:worksheet>
 </file>